--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9">
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -177,7 +177,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.4%</t>
+          <t xml:space="preserve">37.1%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,8 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material Behaviour — https://dkharlanau.github.io/labs/enterprise-context/material-behavior/
+          <t xml:space="preserve">ERP Diagnostic Practice — https://dkharlanau.github.io/labs/erp-diagnostic-practice/
+Material Behaviour — https://dkharlanau.github.io/labs/enterprise-context/material-behavior/
 Master Data — https://dkharlanau.github.io/labs/enterprise-context/master-data/</t>
         </is>
       </c>
@@ -2162,7 +2163,8 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Operations — https://dkharlanau.github.io/labs/enterprise-context/integration-operations/</t>
+          <t xml:space="preserve">ERP Diagnostic Practice — https://dkharlanau.github.io/labs/erp-diagnostic-practice/
+Integration Operations — https://dkharlanau.github.io/labs/enterprise-context/integration-operations/</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -3075,7 +3077,8 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence Coverage — https://dkharlanau.github.io/labs/assessment/evidence-coverage/</t>
+          <t xml:space="preserve">ERP Diagnostic Practice — https://dkharlanau.github.io/labs/erp-diagnostic-practice/
+Evidence Coverage — https://dkharlanau.github.io/labs/assessment/evidence-coverage/</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -4773,22 +4776,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-evaluation, ai-readiness</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-retrieval, ai-evaluation, ai-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -5243,7 +5246,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, logistics-ewm, sales-diagnostics</t>
+          <t xml:space="preserve">delivery-testing, lead-answer, logistics-ewm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5373,7 +5376,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-retrieval, delivery-ams</t>
+          <t xml:space="preserve">ai-agents-mcp, integration-recovery, ai-retrieval</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -7323,7 +7326,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-lifecycle, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -7583,7 +7586,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, ai-readiness, delivery-lifecycle</t>
+          <t xml:space="preserve">integration-recovery, sales-o2c, ai-readiness</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -8233,7 +8236,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, ai-evaluation, delivery-cicd</t>
+          <t xml:space="preserve">ai-data-governance, delivery-testing, ai-evaluation</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -15773,7 +15776,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -18863,17 +18866,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
+          <t xml:space="preserve">Erp Diagnostic Practice</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
+          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -18883,12 +18886,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -18911,7 +18914,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -18923,42 +18926,42 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, integration-cleancore</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -18976,7 +18979,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -18988,42 +18991,42 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/index.md</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -19041,7 +19044,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -19058,17 +19061,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -19083,7 +19086,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -19106,7 +19109,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -19123,17 +19126,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -19148,7 +19151,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -19171,7 +19174,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -19188,17 +19191,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -19213,7 +19216,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -19236,7 +19239,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -19253,17 +19256,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -19278,7 +19281,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -19301,7 +19304,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -19313,22 +19316,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -19343,7 +19346,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -19366,7 +19369,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -19378,42 +19381,42 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -19431,7 +19434,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19448,37 +19451,37 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -19496,7 +19499,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19513,17 +19516,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -19538,7 +19541,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -19561,7 +19564,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -19578,37 +19581,37 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -19626,7 +19629,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19643,17 +19646,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -19673,7 +19676,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -19691,7 +19694,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19708,17 +19711,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -19738,7 +19741,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -19756,7 +19759,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19773,17 +19776,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -19803,7 +19806,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -19821,7 +19824,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19838,17 +19841,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -19868,7 +19871,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -19886,7 +19889,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19903,37 +19906,37 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -19951,7 +19954,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19963,37 +19966,37 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -20003,7 +20006,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J248" t="n">
@@ -20016,7 +20019,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20028,27 +20031,27 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -20058,7 +20061,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -20068,7 +20071,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J249" t="n">
@@ -20081,7 +20084,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20093,37 +20096,37 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/templates/</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/templates/index.md</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -20146,7 +20149,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -20158,70 +20161,135 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>1</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E252" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
+      <c r="F252" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
+      <c r="G252" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J251" t="n">
-        <v>1</v>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L251" t="inlineStr">
+      <c r="I252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>1</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M251"/>
+  <autoFilter ref="A1:M252"/>
 </worksheet>
 </file>
 
@@ -20306,10 +20374,10 @@
         <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -21007,10 +21075,10 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
         <v>21</v>
@@ -22820,17 +22888,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready — Evals and Reliability</t>
+          <t xml:space="preserve">AI Ready Lab — Agent with Approval</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/evals-reliability/</t>
+          <t xml:space="preserve">/labs/ai-ready/labs/agent-approval/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-retrieval, ai-evaluation, ai-readiness</t>
+          <t xml:space="preserve">ai-agents-mcp, ai-security, ai-evaluation</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -22840,7 +22908,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/evals-reliability/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/labs/agent-approval/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -22857,17 +22925,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready Lab — Agent with Approval</t>
+          <t xml:space="preserve">AI Ready Lab — Read-only MCP Workspace</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/labs/agent-approval/</t>
+          <t xml:space="preserve">/labs/ai-ready/labs/mcp-readonly/</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-security, ai-evaluation</t>
+          <t xml:space="preserve">ai-agents-mcp, integration-recovery, ai-evaluation</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -22877,7 +22945,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/labs/agent-approval/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/labs/mcp-readonly/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -22889,22 +22957,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">SAP Production / PP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready Lab — Read-only MCP Workspace</t>
+          <t xml:space="preserve">AI Ready Lab — Production Readiness</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/labs/mcp-readonly/</t>
+          <t xml:space="preserve">/labs/ai-ready/labs/production-readiness/</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, integration-recovery, ai-evaluation</t>
+          <t xml:space="preserve">ai-evaluation, ai-readiness, ai-security</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -22914,7 +22982,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/labs/mcp-readonly/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/labs/production-readiness/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -22926,32 +22994,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Production / PP</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready Lab — Production Readiness</t>
+          <t xml:space="preserve">AI Ready Lab — RAG with Evals</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/labs/production-readiness/</t>
+          <t xml:space="preserve">/labs/ai-ready/labs/rag-evals/</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-evaluation, ai-readiness, ai-security</t>
+          <t xml:space="preserve">ai-retrieval, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/labs/production-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/labs/rag-evals/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -22968,27 +23036,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready Lab — RAG with Evals</t>
+          <t xml:space="preserve">AI Ready Practice — Context Experiment</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/labs/rag-evals/</t>
+          <t xml:space="preserve">/labs/ai-ready/practice/context-experiment/</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-retrieval, ai-agents-mcp, ai-data-governance</t>
+          <t xml:space="preserve">delivery-testing, lead-answer, logistics-ewm</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/labs/rag-evals/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/practice/context-experiment/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -23005,17 +23073,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready Practice — Context Experiment</t>
+          <t xml:space="preserve">AI Ready — Engineering Practice</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/practice/context-experiment/</t>
+          <t xml:space="preserve">/labs/ai-ready/practice/</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, logistics-ewm, sales-diagnostics</t>
+          <t xml:space="preserve">ai-retrieval, ai-agents-mcp, ai-evaluation</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -23025,7 +23093,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/practice/context-experiment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/practice/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -23042,17 +23110,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready — Engineering Practice</t>
+          <t xml:space="preserve">AI Ready Practice — Local Operations Assistant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/practice/</t>
+          <t xml:space="preserve">/labs/ai-ready/practice/local-assistant/</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-retrieval, ai-agents-mcp, ai-evaluation</t>
+          <t xml:space="preserve">ai-agents-mcp, integration-recovery, ai-retrieval</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -23062,7 +23130,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/practice/local-assistant/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -23079,17 +23147,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready Practice — Local Operations Assistant</t>
+          <t xml:space="preserve">AI Ready Practice — Model Selection Benchmark</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/practice/local-assistant/</t>
+          <t xml:space="preserve">/labs/ai-ready/practice/model-benchmark/</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-retrieval, delivery-ams</t>
+          <t xml:space="preserve">ai-readiness, ai-evaluation, ai-security</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -23099,7 +23167,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/practice/local-assistant/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/practice/model-benchmark/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -23116,27 +23184,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready Practice — Model Selection Benchmark</t>
+          <t xml:space="preserve">AI Ready Practice — Retrieval Benchmark</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/practice/model-benchmark/</t>
+          <t xml:space="preserve">/labs/ai-ready/practice/retrieval-benchmark/</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, ai-evaluation, ai-security</t>
+          <t xml:space="preserve">ai-retrieval, ai-security, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/practice/model-benchmark/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/practice/retrieval-benchmark/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -23153,17 +23221,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready Practice — Retrieval Benchmark</t>
+          <t xml:space="preserve">AI Ready — Security and Governance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/practice/retrieval-benchmark/</t>
+          <t xml:space="preserve">/labs/ai-ready/security-governance/</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-retrieval, ai-security, ai-agents-mcp</t>
+          <t xml:space="preserve">ai-security, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -23173,7 +23241,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/practice/retrieval-benchmark/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/security-governance/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -23190,27 +23258,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready — Security and Governance</t>
+          <t xml:space="preserve">AI Ready — System Boundaries</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/security-governance/</t>
+          <t xml:space="preserve">/labs/ai-ready/system-boundaries/</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-security, ai-agents-mcp, ai-data-governance</t>
+          <t xml:space="preserve">ai-security, ai-readiness, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/security-governance/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/system-boundaries/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -23227,17 +23295,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready — System Boundaries</t>
+          <t xml:space="preserve">AI Ready — Tools and MCP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/system-boundaries/</t>
+          <t xml:space="preserve">/labs/ai-ready/tools-mcp/</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-security, ai-readiness, ai-agents-mcp</t>
+          <t xml:space="preserve">ai-agents-mcp, integration-cleancore, integration-patterns</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -23247,7 +23315,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/system-boundaries/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/tools-mcp/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -23264,17 +23332,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready — Tools and MCP</t>
+          <t xml:space="preserve">AI Ready — Practical Use Cases</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/tools-mcp/</t>
+          <t xml:space="preserve">/labs/ai-ready/use-cases/</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, integration-cleancore, integration-patterns</t>
+          <t xml:space="preserve">ai-readiness, ai-agents-mcp, ai-business-value</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -23284,7 +23352,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/tools-mcp/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/use-cases/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -23296,22 +23364,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Ready — Practical Use Cases</t>
+          <t xml:space="preserve">Board</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-ready/use-cases/</t>
+          <t xml:space="preserve">/labs/assessment/board/</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, ai-agents-mcp, ai-business-value</t>
+          <t xml:space="preserve">delivery-lifecycle, integration-ownership, lead-decision</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -23321,7 +23389,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-ready/use-cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/board/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -23338,17 +23406,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Board</t>
+          <t xml:space="preserve">Candidate Semantic Review</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/board/</t>
+          <t xml:space="preserve">/labs/assessment/candidate-semantic-review/</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, integration-ownership, lead-decision</t>
+          <t xml:space="preserve">delivery-lifecycle</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -23358,7 +23426,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/board/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/candidate-semantic-review/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -23375,17 +23443,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candidate Semantic Review</t>
+          <t xml:space="preserve">Core</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/candidate-semantic-review/</t>
+          <t xml:space="preserve">/labs/assessment/core/</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, delivery-release, integration-cleancore</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -23395,7 +23463,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/candidate-semantic-review/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/core/</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -23412,17 +23480,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Core Boundaries</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/core/</t>
+          <t xml:space="preserve">/labs/assessment/core-boundaries/</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-release, integration-cleancore</t>
+          <t xml:space="preserve">delivery-lifecycle</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -23432,7 +23500,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/core/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/core-boundaries/</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -23449,12 +23517,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core Boundaries</t>
+          <t xml:space="preserve">Cross Process</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/core-boundaries/</t>
+          <t xml:space="preserve">/labs/assessment/cross-process/</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -23469,7 +23537,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/core-boundaries/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/cross-process/</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -23481,17 +23549,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cross Process</t>
+          <t xml:space="preserve">Evidence Coverage</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/cross-process/</t>
+          <t xml:space="preserve">/labs/assessment/evidence-coverage/</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -23506,7 +23574,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/cross-process/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/evidence-coverage/</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -23518,17 +23586,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence Coverage</t>
+          <t xml:space="preserve">Factual Review</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/evidence-coverage/</t>
+          <t xml:space="preserve">/labs/assessment/factual-review/</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -23543,7 +23611,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/evidence-coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/factual-review/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -23560,17 +23628,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factual Review</t>
+          <t xml:space="preserve">Feedback</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/factual-review/</t>
+          <t xml:space="preserve">/labs/assessment/feedback/</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, lead-team</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -23580,7 +23648,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/factual-review/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/feedback/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -23597,17 +23665,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feedback</t>
+          <t xml:space="preserve">Findings</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/feedback/</t>
+          <t xml:space="preserve">/labs/assessment/human-review/findings/</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, lead-team</t>
+          <t xml:space="preserve">delivery-lifecycle</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -23617,7 +23685,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/feedback/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/human-review/findings/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -23634,12 +23702,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Findings</t>
+          <t xml:space="preserve">Human Review</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/human-review/findings/</t>
+          <t xml:space="preserve">/labs/assessment/human-review/</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -23654,7 +23722,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/human-review/findings/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/human-review/</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -23671,12 +23739,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human Review</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/human-review/</t>
+          <t xml:space="preserve">/labs/assessment/human-review/secondary/</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -23691,7 +23759,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/human-review/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/human-review/secondary/</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -23708,17 +23776,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">SAP Lead Assessment Lab — Reasoning Routes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/human-review/secondary/</t>
+          <t xml:space="preserve">/labs/assessment/</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">integration-ownership, logistics-p2p, logistics-tm</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -23728,7 +23796,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/human-review/secondary/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -23745,17 +23813,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Lab — Reasoning Routes</t>
+          <t xml:space="preserve">Mock</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/</t>
+          <t xml:space="preserve">/labs/assessment/mock/</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, logistics-p2p, logistics-tm</t>
+          <t xml:space="preserve">delivery-ams, delivery-lifecycle</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -23765,7 +23833,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/mock/</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -23782,17 +23850,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mock</t>
+          <t xml:space="preserve">Practice Engine</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/mock/</t>
+          <t xml:space="preserve">/labs/assessment/practice-engine/</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -23802,7 +23870,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/mock/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/practice-engine/</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -23819,12 +23887,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Practice Engine</t>
+          <t xml:space="preserve">Progress</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/practice-engine/</t>
+          <t xml:space="preserve">/labs/assessment/progress/</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -23839,7 +23907,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/practice-engine/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/progress/</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -23856,12 +23924,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress</t>
+          <t xml:space="preserve">Promotion Readiness</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/progress/</t>
+          <t xml:space="preserve">/labs/assessment/promotion-readiness/</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -23876,7 +23944,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/promotion-readiness/</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -23893,17 +23961,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promotion Readiness</t>
+          <t xml:space="preserve">Decision</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/promotion-readiness/</t>
+          <t xml:space="preserve">/labs/assessment/promotion-review/decision/</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">ai-business-value, delivery-lifecycle, lead-answer</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -23913,7 +23981,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/promotion-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/promotion-review/decision/</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -23930,17 +23998,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decision</t>
+          <t xml:space="preserve">Promotion Review</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/promotion-review/decision/</t>
+          <t xml:space="preserve">/labs/assessment/promotion-review/</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-business-value, delivery-lifecycle, lead-answer</t>
+          <t xml:space="preserve">delivery-lifecycle</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -23950,7 +24018,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/promotion-review/decision/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/promotion-review/</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -23967,12 +24035,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promotion Review</t>
+          <t xml:space="preserve">Question Review</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/promotion-review/</t>
+          <t xml:space="preserve">/labs/assessment/question-review/</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -23987,7 +24055,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/promotion-review/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/question-review/</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -23999,17 +24067,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question Review</t>
+          <t xml:space="preserve">Reasoning Coverage</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/question-review/</t>
+          <t xml:space="preserve">/labs/assessment/reasoning-coverage/</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -24024,7 +24092,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/question-review/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/reasoning-coverage/</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -24036,17 +24104,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reasoning Coverage</t>
+          <t xml:space="preserve">Reasoning Gaps</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/reasoning-coverage/</t>
+          <t xml:space="preserve">/labs/assessment/reasoning-gaps/</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -24061,7 +24129,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/reasoning-coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/reasoning-gaps/</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -24078,17 +24146,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reasoning Gaps</t>
+          <t xml:space="preserve">Review</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/reasoning-gaps/</t>
+          <t xml:space="preserve">/labs/assessment/review/</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-cicd, delivery-lifecycle, lead-readiness</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -24098,7 +24166,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/reasoning-gaps/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/review/</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -24115,17 +24183,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Review</t>
+          <t xml:space="preserve">Sales</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/review/</t>
+          <t xml:space="preserve">/labs/assessment/sales/</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, delivery-lifecycle, lead-readiness</t>
+          <t xml:space="preserve">delivery-lifecycle, logistics-ewm, logistics-tm</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -24135,7 +24203,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/review/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/sales/</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -24152,17 +24220,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales</t>
+          <t xml:space="preserve">SAP Lead Assessment — Start Here</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/sales/</t>
+          <t xml:space="preserve">/labs/assessment/start-here/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, logistics-ewm, logistics-tm</t>
+          <t xml:space="preserve">ai-readiness, delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -24172,7 +24240,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/start-here/</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -24184,22 +24252,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Business AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment — Start Here</t>
+          <t xml:space="preserve">Business AI Implementation Cases — Business AI Lab</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/start-here/</t>
+          <t xml:space="preserve">/labs/business-ai/cases/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-lifecycle, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, delivery-testing, integration-observability</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -24209,7 +24277,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/start-here/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/cases/</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -24226,17 +24294,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Implementation Cases — Business AI Lab</t>
+          <t xml:space="preserve">Document-to-ERP AI Pilot — From PDF to Controlled Transaction</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/cases/</t>
+          <t xml:space="preserve">/labs/business-ai/document-to-erp-ai/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-testing, integration-observability</t>
+          <t xml:space="preserve">integration-recovery, sales-o2c, ai-readiness</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -24246,7 +24314,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/document-to-erp-ai/</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -24263,17 +24331,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Document-to-ERP AI Pilot — From PDF to Controlled Transaction</t>
+          <t xml:space="preserve">Business AI by Enterprise Domain — Business AI Lab</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/document-to-erp-ai/</t>
+          <t xml:space="preserve">/labs/business-ai/domains/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, ai-readiness, delivery-lifecycle</t>
+          <t xml:space="preserve">ai-readiness, integration-cleancore, integration-deployment</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -24283,7 +24351,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/document-to-erp-ai/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/domains/</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -24300,27 +24368,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI by Enterprise Domain — Business AI Lab</t>
+          <t xml:space="preserve">ERP Agent Gateway Pilot — Safe AI Tool Access to Enterprise Systems</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/domains/</t>
+          <t xml:space="preserve">/labs/business-ai/erp-agent-gateway/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-cleancore, integration-deployment</t>
+          <t xml:space="preserve">ai-agents-mcp, ai-security, ai-data-governance</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/erp-agent-gateway/</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -24337,27 +24405,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERP Agent Gateway Pilot — Safe AI Tool Access to Enterprise Systems</t>
+          <t xml:space="preserve">Business AI Assessment Matrix — Process, Autonomy, Risk, KPI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/erp-agent-gateway/</t>
+          <t xml:space="preserve">/labs/business-ai/matrix/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-security, ai-data-governance</t>
+          <t xml:space="preserve">ai-business-value, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/erp-agent-gateway/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/matrix/</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -24374,17 +24442,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Assessment Matrix — Process, Autonomy, Risk, KPI</t>
+          <t xml:space="preserve">Business AI Graph Model — Business AI Lab</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/matrix/</t>
+          <t xml:space="preserve">/labs/business-ai/model/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-business-value, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -24394,7 +24462,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/matrix/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/model/</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -24411,17 +24479,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Graph Model — Business AI Lab</t>
+          <t xml:space="preserve">Open Enterprise AI Research — ERP Evidence, Safety, and Readiness</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/model/</t>
+          <t xml:space="preserve">/labs/business-ai/open-research/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-data-governance, delivery-testing, ai-evaluation</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -24431,7 +24499,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/open-research/</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -24448,17 +24516,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open Enterprise AI Research — ERP Evidence, Safety, and Readiness</t>
+          <t xml:space="preserve">Business AI Patterns — Business AI Lab</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/open-research/</t>
+          <t xml:space="preserve">/labs/business-ai/patterns/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, ai-evaluation, delivery-cicd</t>
+          <t xml:space="preserve">integration-deployment, ai-evaluation, ai-readiness</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -24468,7 +24536,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/open-research/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/patterns/</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -24485,17 +24553,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Patterns — Business AI Lab</t>
+          <t xml:space="preserve">Open Enterprise AI Pilots — ERP, Documents, Agents, and Controls</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/patterns/</t>
+          <t xml:space="preserve">/labs/business-ai/pilots/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, ai-evaluation, ai-readiness</t>
+          <t xml:space="preserve">ai-agents-mcp, ai-readiness, ai-data-governance</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -24505,7 +24573,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/patterns/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/pilots/</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -24522,17 +24590,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open Enterprise AI Pilots — ERP, Documents, Agents, and Controls</t>
+          <t xml:space="preserve">Business AI Best Practices and Anti-Patterns</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/pilots/</t>
+          <t xml:space="preserve">/labs/business-ai/practices/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-readiness, ai-data-governance</t>
+          <t xml:space="preserve">ai-readiness, ai-business-value, ai-evaluation</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -24542,7 +24610,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/pilots/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/practices/</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -24559,17 +24627,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Best Practices and Anti-Patterns</t>
+          <t xml:space="preserve">Enterprise Processes for Business AI — Business AI Lab</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/practices/</t>
+          <t xml:space="preserve">/labs/business-ai/processes/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, ai-business-value, ai-evaluation</t>
+          <t xml:space="preserve">ai-readiness, delivery-observability, integration-observability</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -24579,7 +24647,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/practices/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/processes/</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -24596,17 +24664,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Processes for Business AI — Business AI Lab</t>
+          <t xml:space="preserve">Business AI Scenarios — Successes, Mixed Results, Failures</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/processes/</t>
+          <t xml:space="preserve">/labs/business-ai/scenarios/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-observability, integration-observability</t>
+          <t xml:space="preserve">delivery-testing, ai-readiness, delivery-memory</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -24616,7 +24684,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/scenarios/</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -24633,27 +24701,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Scenarios — Successes, Mixed Results, Failures</t>
+          <t xml:space="preserve">Enterprise AI Technology Landscape — Business AI Lab</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/scenarios/</t>
+          <t xml:space="preserve">/labs/business-ai/technologies/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, ai-readiness, delivery-memory</t>
+          <t xml:space="preserve">integration-cleancore, integration-deployment, integration-ownership</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/scenarios/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/technologies/</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -24665,22 +24733,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI</t>
+          <t xml:space="preserve">SAP AIF</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise AI Technology Landscape — Business AI Lab</t>
+          <t xml:space="preserve">Aif</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/technologies/</t>
+          <t xml:space="preserve">/labs/enterprise-context/aif/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, integration-deployment, integration-ownership</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -24690,7 +24758,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/technologies/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/aif/</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -24702,17 +24770,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP AIF</t>
+          <t xml:space="preserve">SAP Automotive JIT/JIS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aif</t>
+          <t xml:space="preserve">Automotive Jit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/aif/</t>
+          <t xml:space="preserve">/labs/enterprise-context/automotive-jit/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -24727,7 +24795,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/aif/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/automotive-jit/</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -24739,32 +24807,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Automotive JIT/JIS</t>
+          <t xml:space="preserve">Business AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automotive Jit</t>
+          <t xml:space="preserve">Agents</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/automotive-jit/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-agents-mcp, delivery-cicd</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/automotive-jit/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -24781,12 +24849,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agents</t>
+          <t xml:space="preserve">Terminology</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/terminology/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -24801,7 +24869,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/terminology/</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -24818,27 +24886,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminology</t>
+          <t xml:space="preserve">SAP Business AI and AI Platform Landscape — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/terminology/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-ai/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, delivery-cicd</t>
+          <t xml:space="preserve">integration-cleancore, ai-agents-mcp, delivery-release</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/terminology/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -24850,32 +24918,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Business AI and AI Platform Landscape — Enterprise Context Lab</t>
+          <t xml:space="preserve">Business Partner</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-ai/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-partner/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, ai-agents-mcp, delivery-release</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-partner/</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -24887,32 +24955,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">Condition Contract Management</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner</t>
+          <t xml:space="preserve">Procurement</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-partner/</t>
+          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/procurement/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-p2p</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-partner/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/procurement/</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -24929,27 +24997,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procurement</t>
+          <t xml:space="preserve">Sales</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/sales/</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p</t>
+          <t xml:space="preserve">logistics-ewm, logistics-tm, sales-diagnostics</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/sales/</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -24961,32 +25029,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Condition Contract Management</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales</t>
+          <t xml:space="preserve">Decisions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/aatp-prioritization.html</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-ewm, logistics-tm, sales-diagnostics</t>
+          <t xml:space="preserve">integration-deployment, logistics-mdg, logistics-p2p</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/aatp-prioritization.html</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -25008,7 +25076,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/aatp-prioritization.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -25023,7 +25091,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/aatp-prioritization.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -25035,7 +25103,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -25045,7 +25113,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -25060,7 +25128,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -25072,7 +25140,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -25082,7 +25150,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -25097,7 +25165,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -25119,7 +25187,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -25134,7 +25202,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -25156,7 +25224,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -25171,7 +25239,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -25183,7 +25251,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP EWM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -25193,7 +25261,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -25208,7 +25276,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -25220,7 +25288,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP EWM</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -25230,7 +25298,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/grir-ownership.html</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -25245,7 +25313,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/grir-ownership.html</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -25257,7 +25325,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">Integration Operations</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -25267,7 +25335,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/grir-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-api-event.html</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -25282,7 +25350,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/grir-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-api-event.html</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -25304,7 +25372,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-api-event.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -25319,7 +25387,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-api-event.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -25331,7 +25399,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Operations</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -25341,7 +25409,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -25356,7 +25424,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -25368,7 +25436,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -25378,7 +25446,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/master-data-validation.html</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -25393,7 +25461,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/master-data-validation.html</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -25405,7 +25473,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -25415,7 +25483,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/master-data-validation.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -25430,7 +25498,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/master-data-validation.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -25452,7 +25520,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/po-change-impact.html</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -25467,7 +25535,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/po-change-impact.html</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -25479,7 +25547,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -25489,7 +25557,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/po-change-impact.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/pricing-ownership.html</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -25504,7 +25572,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/po-change-impact.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/pricing-ownership.html</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -25516,7 +25584,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -25526,7 +25594,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/pricing-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/retry-idempotency.html</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -25541,7 +25609,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/pricing-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/retry-idempotency.html</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -25563,7 +25631,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/retry-idempotency.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -25578,7 +25646,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/retry-idempotency.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -25600,7 +25668,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/source-selection-ownership.html</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -25615,7 +25683,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/source-selection-ownership.html</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -25637,7 +25705,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/source-selection-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -25652,7 +25720,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/source-selection-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -25674,7 +25742,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -25689,7 +25757,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -25701,7 +25769,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -25711,7 +25779,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/tax-ownership.html</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -25726,7 +25794,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/tax-ownership.html</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -25738,22 +25806,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">ABAP / Extensibility</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decisions</t>
+          <t xml:space="preserve">ABAP Runtime and UI Toolkit — BAL, ALV, SALV and Fiori</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/tax-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, logistics-mdg, logistics-p2p</t>
+          <t xml:space="preserve">integration-development, lead-answer, sales-billing</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -25763,7 +25831,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/tax-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -25780,17 +25848,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABAP Runtime and UI Toolkit — BAL, ALV, SALV and Fiori</t>
+          <t xml:space="preserve">SAP Development Toolbox — Frameworks, Quality and Delivery</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
+          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-development, lead-answer, sales-billing</t>
+          <t xml:space="preserve">ai-data-governance, delivery-cicd, delivery-lifecycle</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -25800,7 +25868,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -25812,32 +25880,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABAP / Extensibility</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Development Toolbox — Frameworks, Quality and Delivery</t>
+          <t xml:space="preserve">Enterprise Business Domains — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/</t>
+          <t xml:space="preserve">/labs/enterprise-context/domains/</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, delivery-cicd, delivery-lifecycle</t>
+          <t xml:space="preserve">integration-ownership, integration-deployment, logistics-mdg</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/domains/</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -25849,22 +25917,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP EWM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Business Domains — Enterprise Context Lab</t>
+          <t xml:space="preserve">Automation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/domains/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/automation/</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, integration-deployment, logistics-mdg</t>
+          <t xml:space="preserve">ai-data-governance, logistics-ewm</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -25874,7 +25942,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/automation/</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -25891,27 +25959,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automation</t>
+          <t xml:space="preserve">Controls</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/automation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/controls/</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, logistics-ewm</t>
+          <t xml:space="preserve">ai-readiness, logistics-ewm</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/automation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/controls/</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -25928,27 +25996,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Controls</t>
+          <t xml:space="preserve">Domains</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/controls/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/domains/</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, logistics-ewm</t>
+          <t xml:space="preserve">logistics-ewm</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/controls/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/domains/</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -25965,12 +26033,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domains</t>
+          <t xml:space="preserve">Handling Units Packing</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/domains/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/handling-units-packing/</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -25985,7 +26053,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/handling-units-packing/</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -26002,27 +26070,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handling Units Packing</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/handling-units-packing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/integrations/</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-ewm</t>
+          <t xml:space="preserve">integration-patterns, logistics-ewm</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/handling-units-packing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/integrations/</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -26039,17 +26107,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Interfaces</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/interfaces/</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, logistics-ewm</t>
+          <t xml:space="preserve">delivery-testing, logistics-ewm</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -26059,7 +26127,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/interfaces/</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -26076,27 +26144,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interfaces</t>
+          <t xml:space="preserve">Mobility</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/interfaces/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/mobility/</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, logistics-ewm</t>
+          <t xml:space="preserve">logistics-ewm</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/interfaces/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/mobility/</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -26113,12 +26181,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobility</t>
+          <t xml:space="preserve">Objects</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/mobility/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/objects/</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -26133,7 +26201,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/mobility/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/objects/</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -26150,12 +26218,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objects</t>
+          <t xml:space="preserve">Scanners</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/objects/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/scanners/</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -26170,7 +26238,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/objects/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/scanners/</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -26182,22 +26250,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP EWM</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanners</t>
+          <t xml:space="preserve">Finance Logistics</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/scanners/</t>
+          <t xml:space="preserve">/labs/enterprise-context/finance-logistics/</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-ewm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -26207,7 +26275,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/scanners/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/finance-logistics/</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -26219,32 +26287,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finance Logistics</t>
+          <t xml:space="preserve">BRFplus, AIF and ISLM — Decision, Recovery and AI Lifecycle</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/finance-logistics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/frameworks/</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, delivery-cicd, integration-cleancore</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/finance-logistics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/frameworks/</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -26261,17 +26329,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRFplus, AIF and ISLM — Decision, Recovery and AI Lifecycle</t>
+          <t xml:space="preserve">Enterprise Context Lab — Process, Data, Rules and AI Reasoning</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/frameworks/</t>
+          <t xml:space="preserve">/labs/enterprise-context/</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-cicd, integration-cleancore</t>
+          <t xml:space="preserve">integration-ownership, delivery-testing, integration-patterns</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -26281,7 +26349,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/frameworks/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -26298,17 +26366,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Process, Data, Rules and AI Reasoning</t>
+          <t xml:space="preserve">SAP Industry Solutions — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/</t>
+          <t xml:space="preserve">/labs/enterprise-context/industries/</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, delivery-testing, integration-patterns</t>
+          <t xml:space="preserve">logistics-production-quality, ai-readiness, delivery-observability</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -26318,7 +26386,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/industries/</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -26330,22 +26398,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Industry Solutions — Enterprise Context Lab</t>
+          <t xml:space="preserve">Data Migration</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/industries/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/data-migration/</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality, ai-readiness, delivery-observability</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -26355,7 +26423,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/industries/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/data-migration/</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -26367,32 +26435,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Migration</t>
+          <t xml:space="preserve">Iot Devices</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/data-migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/iot-devices/</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/data-migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/iot-devices/</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -26404,32 +26472,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iot Devices</t>
+          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/iot-devices/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/iot-devices/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -26446,17 +26514,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
+          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -26466,7 +26534,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -26483,17 +26551,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
+          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -26503,7 +26571,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -26520,17 +26588,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -26540,7 +26608,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -26557,27 +26625,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
+          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -26589,32 +26657,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
+          <t xml:space="preserve">integration-observability, delivery-release, integration-deployment</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -26626,32 +26694,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, delivery-release, integration-deployment</t>
+          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -26668,27 +26736,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
+          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -26705,17 +26773,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -26725,7 +26793,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -26742,17 +26810,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
+          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -26762,7 +26830,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -26779,27 +26847,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -26816,27 +26884,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
+          <t xml:space="preserve">integration-patterns, logistics-mdg, delivery-testing</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -26853,17 +26921,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, logistics-mdg, delivery-testing</t>
+          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -26873,7 +26941,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -26885,22 +26953,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
+          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -26910,7 +26978,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -26927,17 +26995,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
+          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -26947,7 +27015,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -26959,22 +27027,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
+          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -26984,7 +27052,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -27001,17 +27069,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
+          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-mdg</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -27021,7 +27089,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -27038,27 +27106,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-mdg</t>
+          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -27075,27 +27143,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -27112,17 +27180,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing, ai-agents-mcp</t>
+          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -27132,7 +27200,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -27144,32 +27212,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
+          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
+          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -27181,32 +27249,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
+          <t xml:space="preserve">Anatomy</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -27223,12 +27291,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anatomy</t>
+          <t xml:space="preserve">Casebook</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -27243,7 +27311,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -27260,17 +27328,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casebook</t>
+          <t xml:space="preserve">Configuration</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -27280,7 +27348,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -27297,17 +27365,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuration</t>
+          <t xml:space="preserve">Operations</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
+          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27317,7 +27385,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -27334,17 +27402,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operations</t>
+          <t xml:space="preserve">Scenarios</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27354,7 +27422,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -27366,22 +27434,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenarios</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -27391,7 +27459,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -27403,32 +27471,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -27440,17 +27508,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27465,7 +27533,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -27482,12 +27550,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27502,7 +27570,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -27519,12 +27587,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -27539,7 +27607,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -27556,27 +27624,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -27588,22 +27656,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -27613,7 +27681,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -27625,32 +27693,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -27662,32 +27730,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -27704,12 +27772,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -27724,7 +27792,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -27736,17 +27804,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -27761,7 +27829,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -27773,17 +27841,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -27798,7 +27866,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -27810,32 +27878,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -27847,32 +27915,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -27884,32 +27952,32 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -27921,22 +27989,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, integration-cleancore</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -27946,7 +28014,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -27963,17 +28031,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -27983,7 +28051,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -28000,17 +28068,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28020,7 +28088,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -28037,17 +28105,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28057,7 +28125,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -28074,17 +28142,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -28094,7 +28162,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -28111,17 +28179,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28131,7 +28199,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -28143,32 +28211,32 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -28180,32 +28248,32 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -28214,45 +28282,8 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooling / Roadmap</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/labs/tool-roadmap/</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G160"/>
+  <autoFilter ref="A1:G159"/>
 </worksheet>
 </file>
 

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9">
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.1%</t>
+          <t xml:space="preserve">37.3%</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,8 @@
         <is>
           <t xml:space="preserve">ERP Diagnostic Practice — https://dkharlanau.github.io/labs/erp-diagnostic-practice/
 Material Behaviour — https://dkharlanau.github.io/labs/enterprise-context/material-behavior/
-Master Data — https://dkharlanau.github.io/labs/enterprise-context/master-data/</t>
+Master Data — https://dkharlanau.github.io/labs/enterprise-context/master-data/
+Business Partner API — https://dkharlanau.github.io/labs/enterprise-context/integrations/business-partner-api/</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2098,7 +2099,8 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations — https://dkharlanau.github.io/labs/enterprise-context/integrations/</t>
+          <t xml:space="preserve">Integrations — https://dkharlanau.github.io/labs/enterprise-context/integrations/
+Business Partner API — https://dkharlanau.github.io/labs/enterprise-context/integrations/business-partner-api/</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -2164,7 +2166,8 @@
       <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">ERP Diagnostic Practice — https://dkharlanau.github.io/labs/erp-diagnostic-practice/
-Integration Operations — https://dkharlanau.github.io/labs/enterprise-context/integration-operations/</t>
+Integration Operations — https://dkharlanau.github.io/labs/enterprise-context/integration-operations/
+Business Partner API — https://dkharlanau.github.io/labs/enterprise-context/integrations/business-partner-api/</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -13011,42 +13014,42 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Migration</t>
+          <t xml:space="preserve">SAP Business Partner API — Data Model, Segments, CVI and Integration Design</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/data-migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/business-partner-api/</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integrations/data-migration/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/business-partner-api/index.md</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -13064,7 +13067,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/data-migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/business-partner-api/</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13081,37 +13084,37 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP DRF — Data Replication Framework</t>
+          <t xml:space="preserve">Data Migration</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/drf/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/data-migration/</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integrations/drf/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/data-migration/index.html</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -13129,7 +13132,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/drf/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/data-migration/</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13146,17 +13149,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Integration Architecture — Logistics, Events and Data Distribution</t>
+          <t xml:space="preserve">SAP DRF — Data Replication Framework</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/drf/</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integrations/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/drf/index.md</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13166,12 +13169,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -13194,7 +13197,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/drf/</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13206,22 +13209,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Inventory Management</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inventory Management</t>
+          <t xml:space="preserve">SAP Integration Architecture — Logistics, Events and Data Distribution</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/inventory-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/inventory-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/index.md</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13236,7 +13239,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-inventory</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -13259,7 +13262,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/inventory-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13271,27 +13274,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Inventory Management</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iot Devices</t>
+          <t xml:space="preserve">Inventory Management</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/iot-devices/</t>
+          <t xml:space="preserve">/labs/enterprise-context/inventory-management/</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/iot-devices/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/inventory-management/index.html</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -13301,7 +13304,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-inventory</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -13311,7 +13314,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -13324,7 +13327,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/iot-devices/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/inventory-management/</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13336,27 +13339,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Kanban</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Cycle</t>
+          <t xml:space="preserve">Iot Devices</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/control-cycle/</t>
+          <t xml:space="preserve">/labs/enterprise-context/iot-devices/</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/control-cycle/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/iot-devices/index.html</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -13366,7 +13369,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -13389,7 +13392,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/control-cycle/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/iot-devices/</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13406,17 +13409,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kanban</t>
+          <t xml:space="preserve">Control Cycle</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/control-cycle/</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/control-cycle/index.html</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13454,7 +13457,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/control-cycle/</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -13471,17 +13474,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operations Diagnostics</t>
+          <t xml:space="preserve">Kanban</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/operations-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/operations-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/index.html</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13496,7 +13499,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-inventory</t>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -13506,7 +13509,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -13519,7 +13522,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/operations-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -13536,17 +13539,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull Control</t>
+          <t xml:space="preserve">Operations Diagnostics</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/pull-control/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/operations-diagnostics/</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/pull-control/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/operations-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13561,7 +13564,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">logistics-inventory</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -13571,7 +13574,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -13584,7 +13587,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/pull-control/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/operations-diagnostics/</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -13601,17 +13604,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Replenishment Strategies</t>
+          <t xml:space="preserve">Pull Control</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/replenishment-strategies/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/pull-control/</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/replenishment-strategies/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/pull-control/index.html</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13626,7 +13629,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p</t>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -13636,7 +13639,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -13649,7 +13652,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/replenishment-strategies/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/pull-control/</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -13666,17 +13669,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Runtime Flows</t>
+          <t xml:space="preserve">Replenishment Strategies</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/runtime-flows/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/replenishment-strategies/</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/runtime-flows/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/replenishment-strategies/index.html</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13714,7 +13717,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/runtime-flows/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/replenishment-strategies/</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -13731,17 +13734,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statuses Signals</t>
+          <t xml:space="preserve">Runtime Flows</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/statuses-signals/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/runtime-flows/</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/statuses-signals/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/runtime-flows/index.html</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13756,7 +13759,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-inventory</t>
+          <t xml:space="preserve">logistics-p2p</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -13779,7 +13782,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/statuses-signals/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/runtime-flows/</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -13791,22 +13794,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP Kanban</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logistics Capabilities</t>
+          <t xml:space="preserve">Statuses Signals</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/logistics-capabilities/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/statuses-signals/</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/logistics-capabilities/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/statuses-signals/index.html</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13821,7 +13824,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership</t>
+          <t xml:space="preserve">logistics-inventory</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -13831,7 +13834,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -13844,7 +13847,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/logistics-capabilities/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/statuses-signals/</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -13856,22 +13859,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Logistics Capabilities</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/logistics-capabilities/</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/logistics-capabilities/index.html</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13886,7 +13889,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data</t>
+          <t xml:space="preserve">integration-ownership</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -13896,7 +13899,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -13909,7 +13912,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/logistics-capabilities/</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -13926,17 +13929,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material Behavior</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/material-behavior/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/material-behavior/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/index.html</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13974,7 +13977,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/material-behavior/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -13986,27 +13989,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
+          <t xml:space="preserve">Material Behavior</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">/labs/enterprise-context/material-behavior/</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/architecture/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/material-behavior/index.html</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -14016,12 +14019,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -14039,7 +14042,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/material-behavior/</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14056,37 +14059,37 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lead Assessment Drills — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/assessment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/assessment/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/architecture/index.md</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, lead-decision, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -14104,7 +14107,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/assessment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -14121,37 +14124,37 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Lead Assessment Drills — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/assessment/</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/build-runtime/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/assessment/index.md</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, lead-decision, logistics-mdg</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -14169,7 +14172,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/assessment/</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -14186,37 +14189,37 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Consolidation &amp; Golden Record — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/build-runtime/index.md</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14234,7 +14237,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -14251,17 +14254,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Matching &amp; Survivorship — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Consolidation &amp; Golden Record — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/survivorship/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/survivorship/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/index.md</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14299,7 +14302,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/survivorship/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -14316,37 +14319,37 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Matching &amp; Survivorship — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/survivorship/</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/engineering/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/survivorship/index.md</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14364,7 +14367,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/survivorship/</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -14381,17 +14384,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/engineering/index.md</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14411,7 +14414,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
+          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -14429,7 +14432,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -14446,17 +14449,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/deployments/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/index.md</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14476,12 +14479,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -14494,7 +14497,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -14506,22 +14509,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/entity-map/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/deployments/index.md</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14541,12 +14544,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, delivery-release, integration-deployment</t>
+          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -14559,7 +14562,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -14576,37 +14579,37 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner, Customer &amp; Supplier — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/entity-map/index.md</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, delivery-release</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -14624,7 +14627,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -14636,22 +14639,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Domain Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Business Partner, Customer &amp; Supplier — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/index.md</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14666,7 +14669,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg, sales-o2c</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -14689,7 +14692,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -14706,42 +14709,42 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Domain Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/entity-map/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/index.md</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -14754,7 +14757,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -14771,42 +14774,42 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Domain — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/entity-map/index.md</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -14819,7 +14822,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -14836,37 +14839,37 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Material Domain — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/extensions/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/index.md</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14884,7 +14887,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -14901,17 +14904,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/brfplus-rules/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/extensions/index.md</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14931,7 +14934,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -14949,7 +14952,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -14966,37 +14969,37 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Change Request Type Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/change-request-matrix/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/brfplus-rules/index.md</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-decision, logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -15014,7 +15017,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -15031,17 +15034,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Engine — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Change Request Type Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/change-request-matrix/index.md</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15079,7 +15082,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -15096,37 +15099,37 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Governance Engine — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/impact/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/index.md</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-decision, logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15144,7 +15147,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -15161,17 +15164,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
+          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/implementation/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/impact/index.md</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15191,12 +15194,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
+          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -15209,7 +15212,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -15221,27 +15224,27 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Governance</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data Governance — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/implementation/index.md</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -15251,17 +15254,17 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -15274,7 +15277,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15286,27 +15289,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Data Governance</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP Master Data Governance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/interfaces/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/index.md</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -15316,17 +15319,17 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, logistics-mdg, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J176" t="n">
@@ -15339,7 +15342,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15356,17 +15359,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/lineage/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/interfaces/index.md</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -15386,7 +15389,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -15404,7 +15407,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -15416,22 +15419,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/cases/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/lineage/index.md</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -15451,7 +15454,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
+          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -15469,7 +15472,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -15486,17 +15489,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/cases/index.md</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -15516,7 +15519,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
+          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -15534,7 +15537,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -15546,22 +15549,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/migration/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/index.md</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -15581,7 +15584,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">logistics-master-data, sales-o2c, logistics-tm</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -15599,7 +15602,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -15616,17 +15619,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/ownership/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/migration/index.md</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -15646,7 +15649,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-mdg</t>
+          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -15664,7 +15667,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -15681,17 +15684,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
+          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/processes/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/ownership/index.md</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -15711,12 +15714,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
+          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-master-data</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -15729,7 +15732,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -15746,17 +15749,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/reasoning/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/processes/index.md</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -15776,12 +15779,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
+          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -15794,7 +15797,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -15811,37 +15814,37 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Replication &amp; Distribution — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/replication/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/reasoning/index.md</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -15859,7 +15862,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -15876,17 +15879,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG DRF Operations &amp; Replay — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Replication &amp; Distribution — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/replication/operations/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/replication/index.md</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -15901,7 +15904,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -15924,7 +15927,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -15941,37 +15944,37 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG DRF Operations &amp; Replay — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/operations/</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/scenario/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/replication/operations/index.md</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -15989,7 +15992,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/operations/</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -16001,42 +16004,42 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA API-Led Migration — Design, Restart and Cutover</t>
+          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/api-led-migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/api-led-migration.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/scenario/index.md</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-patterns, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -16054,7 +16057,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/api-led-migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -16071,17 +16074,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Cutover — Rehearsal, Delta and Reconciliation</t>
+          <t xml:space="preserve">SAP S/4HANA API-Led Migration — Design, Restart and Cutover</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/cutover/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/api-led-migration/</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/cutover.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/api-led-migration.md</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -16096,7 +16099,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-recovery, logistics-inventory</t>
+          <t xml:space="preserve">delivery-release, integration-patterns, integration-recovery</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -16119,7 +16122,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/cutover/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/api-led-migration/</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -16136,17 +16139,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Design Register — Object Control</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Cutover — Rehearsal, Delta and Reconciliation</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/design-register/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/cutover/</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/design-register.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/cutover.md</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -16161,7 +16164,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
+          <t xml:space="preserve">delivery-release, integration-recovery, logistics-inventory</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -16184,7 +16187,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/design-register/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/cutover/</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -16201,17 +16204,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Domain Playbooks — SD, MM, PP, EWM, FI and CO</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Design Register — Object Control</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/domain-playbooks/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/design-register/</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/domain-playbooks.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/design-register.md</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -16226,7 +16229,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, logistics-production-quality, sales-o2c</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -16249,7 +16252,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/domain-playbooks/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/design-register/</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -16266,17 +16269,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Greenfield Migration — Architecture and Data Load</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Domain Playbooks — SD, MM, PP, EWM, FI and CO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/domain-playbooks/</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/domain-playbooks.md</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -16291,7 +16294,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, logistics-master-data</t>
+          <t xml:space="preserve">logistics-p2p, logistics-production-quality, sales-o2c</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -16314,7 +16317,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/domain-playbooks/</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -16331,17 +16334,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Lead Assessment — Architecture Drills</t>
+          <t xml:space="preserve">SAP S/4HANA Greenfield Migration — Architecture and Data Load</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/lead-assessment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/lead-assessment.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/index.md</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -16356,7 +16359,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, logistics-master-data</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -16379,7 +16382,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/lead-assessment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -16396,17 +16399,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Factory — Governance, Mock Cycles and Ownership</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Lead Assessment — Architecture Drills</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/migration-factory/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/lead-assessment/</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/migration-factory.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/lead-assessment.md</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -16421,7 +16424,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-recovery, lead-decision</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -16444,7 +16447,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/migration-factory/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/lead-assessment/</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -16461,17 +16464,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Object Catalog — Greenfield Load Scope</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Factory — Governance, Mock Cycles and Ownership</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/object-catalog/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/migration-factory/</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/object-catalog.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/migration-factory.md</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -16486,7 +16489,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-release, integration-recovery, lead-decision</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -16509,7 +16512,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/object-catalog/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/migration-factory/</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -16526,17 +16529,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Tools — Cockpit, APIs and Integration</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Object Catalog — Greenfield Load Scope</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/tooling/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/object-catalog/</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/tooling.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/object-catalog.md</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -16551,7 +16554,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, integration-deployment, integration-patterns</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -16574,7 +16577,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/tooling/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/object-catalog/</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -16586,47 +16589,47 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Tools — Cockpit, APIs and Integration</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/tooling/</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/model/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/tooling.md</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-cicd, integration-deployment, integration-patterns</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J196" t="n">
@@ -16639,7 +16642,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/tooling/</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -16651,47 +16654,47 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Performance</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Performance and Technical Operations — Practical S/4HANA Troubleshooting</t>
+          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/performance/</t>
+          <t xml:space="preserve">/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/performance/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/model/index.md</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-observability, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J197" t="n">
@@ -16704,7 +16707,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/performance/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -16716,42 +16719,42 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP Performance</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anatomy</t>
+          <t xml:space="preserve">SAP Performance and Technical Operations — Practical S/4HANA Troubleshooting</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">/labs/enterprise-context/performance/</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/anatomy/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/performance/index.md</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-observability, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -16769,7 +16772,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/performance/</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -16786,17 +16789,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casebook</t>
+          <t xml:space="preserve">Anatomy</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/casebook/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/anatomy/index.html</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -16834,7 +16837,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -16851,17 +16854,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuration</t>
+          <t xml:space="preserve">Casebook</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/configuration/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/casebook/index.html</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -16881,7 +16884,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -16899,7 +16902,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -16916,22 +16919,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pricing</t>
+          <t xml:space="preserve">Configuration</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/configuration/index.html</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -16941,12 +16944,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -16964,7 +16967,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -16981,22 +16984,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operations</t>
+          <t xml:space="preserve">Pricing</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/operations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/index.html</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -17006,12 +17009,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -17029,7 +17032,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -17046,17 +17049,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenarios</t>
+          <t xml:space="preserve">Operations</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/scenarios/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/operations/index.html</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -17076,7 +17079,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -17094,7 +17097,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -17106,27 +17109,27 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Procurement / MM</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procurement</t>
+          <t xml:space="preserve">Scenarios</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/scenarios/index.html</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -17136,12 +17139,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -17159,7 +17162,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -17176,17 +17179,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
+          <t xml:space="preserve">Procurement</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/index.html</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -17196,12 +17199,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">logistics-p2p</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -17224,7 +17227,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -17241,17 +17244,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -17266,7 +17269,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -17289,7 +17292,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -17306,17 +17309,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -17331,7 +17334,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -17354,7 +17357,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -17371,17 +17374,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -17396,7 +17399,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -17419,7 +17422,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -17436,17 +17439,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -17461,7 +17464,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -17484,7 +17487,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -17496,22 +17499,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Production / PP</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production</t>
+          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -17521,12 +17524,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -17536,7 +17539,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -17549,7 +17552,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -17561,22 +17564,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Quality Management</t>
+          <t xml:space="preserve">SAP Production / PP</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality Management</t>
+          <t xml:space="preserve">Production</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -17614,7 +17617,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -17626,27 +17629,27 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Quality Management</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Quality Management</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -17656,17 +17659,17 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -17679,7 +17682,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -17691,22 +17694,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -17726,12 +17729,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J213" t="n">
@@ -17744,7 +17747,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -17756,27 +17759,27 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Diagnostics</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -17786,7 +17789,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-diagnostics</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -17809,7 +17812,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -17826,22 +17829,22 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Sales Diagnostics</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -17851,7 +17854,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -17874,7 +17877,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -17891,17 +17894,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -17939,7 +17942,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -17956,17 +17959,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -18004,7 +18007,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -18021,17 +18024,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -18051,12 +18054,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J218" t="n">
@@ -18069,7 +18072,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -18086,22 +18089,22 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Processes</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -18111,12 +18114,12 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -18134,7 +18137,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -18146,27 +18149,27 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Sales Processes</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -18176,12 +18179,12 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -18199,7 +18202,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -18211,22 +18214,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -18246,12 +18249,12 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J221" t="n">
@@ -18264,7 +18267,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -18276,22 +18279,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -18311,12 +18314,12 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J222" t="n">
@@ -18329,7 +18332,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -18346,17 +18349,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -18394,7 +18397,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -18406,27 +18409,27 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Shipping</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -18436,7 +18439,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -18446,7 +18449,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J224" t="n">
@@ -18459,7 +18462,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -18471,27 +18474,27 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP Shipping</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Shipping</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -18501,7 +18504,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-shipping</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -18511,7 +18514,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J225" t="n">
@@ -18524,7 +18527,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -18536,37 +18539,37 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -18576,7 +18579,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J226" t="n">
@@ -18589,7 +18592,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -18601,37 +18604,37 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -18641,7 +18644,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J227" t="n">
@@ -18654,7 +18657,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -18671,22 +18674,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Management</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -18696,7 +18699,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -18719,7 +18722,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -18731,27 +18734,27 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Transportation Management</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -18761,17 +18764,17 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J229" t="n">
@@ -18784,7 +18787,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -18796,22 +18799,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -18831,12 +18834,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J230" t="n">
@@ -18849,7 +18852,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -18861,27 +18864,27 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erp Diagnostic Practice</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -18891,17 +18894,17 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J231" t="n">
@@ -18914,7 +18917,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -18931,17 +18934,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
+          <t xml:space="preserve">Erp Diagnostic Practice</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
+          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -18951,12 +18954,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -18979,7 +18982,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -18991,42 +18994,42 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -19044,7 +19047,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -19056,42 +19059,42 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/index.md</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -19109,7 +19112,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -19126,17 +19129,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -19151,7 +19154,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -19174,7 +19177,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -19191,17 +19194,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -19216,7 +19219,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -19239,7 +19242,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -19256,17 +19259,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -19281,7 +19284,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -19304,7 +19307,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -19321,17 +19324,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -19346,7 +19349,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -19369,7 +19372,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -19381,22 +19384,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19411,7 +19414,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -19434,7 +19437,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19446,42 +19449,42 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -19499,7 +19502,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19516,37 +19519,37 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -19564,7 +19567,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -19581,17 +19584,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -19606,7 +19609,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -19629,7 +19632,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19646,37 +19649,37 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -19694,7 +19697,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19711,17 +19714,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -19741,7 +19744,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -19759,7 +19762,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19776,17 +19779,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -19806,7 +19809,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -19824,7 +19827,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19841,17 +19844,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -19871,7 +19874,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -19889,7 +19892,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19906,17 +19909,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -19936,7 +19939,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -19954,7 +19957,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19971,37 +19974,37 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -20019,7 +20022,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20031,37 +20034,37 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -20071,7 +20074,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J249" t="n">
@@ -20084,7 +20087,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20096,27 +20099,27 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -20126,7 +20129,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -20136,7 +20139,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J250" t="n">
@@ -20149,7 +20152,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -20161,37 +20164,37 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/templates/</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/templates/index.md</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -20214,7 +20217,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -20226,70 +20229,135 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>1</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C253" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
+      <c r="F253" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
+      <c r="G253" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J252" t="n">
-        <v>1</v>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L252" t="inlineStr">
+      <c r="I253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>1</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M252"/>
+  <autoFilter ref="A1:M253"/>
 </worksheet>
 </file>
 
@@ -20701,10 +20769,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -26672,7 +26740,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, delivery-release, integration-deployment</t>
+          <t xml:space="preserve">integration-observability, integration-recovery, delivery-release</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -26894,7 +26962,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, logistics-mdg, delivery-testing</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -27005,7 +27073,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
+          <t xml:space="preserve">logistics-master-data, sales-o2c, logistics-tm</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -27079,7 +27147,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-mdg</t>
+          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-master-data</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -177,7 +177,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.3%</t>
+          <t xml:space="preserve">38.1%</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,9 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Processes — https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">Sales Processes — https://dkharlanau.github.io/labs/enterprise-context/sales-processes/
+Sales Organizational Context &amp; Master Data — https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/
+Sales Lead Assessment Map — https://dkharlanau.github.io/labs/assessment/sales/</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -5899,7 +5901,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -6029,7 +6031,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -6094,7 +6096,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -6159,7 +6161,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -6224,7 +6226,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -6289,7 +6291,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, lead-team</t>
+          <t xml:space="preserve">delivery-lifecycle, lead-team, sales-o2c</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -6354,7 +6356,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -6419,7 +6421,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -6484,7 +6486,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6614,7 +6616,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-ams, delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6679,7 +6681,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6744,7 +6746,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6809,7 +6811,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6939,7 +6941,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7004,7 +7006,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7069,7 +7071,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7134,7 +7136,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -7249,7 +7251,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7259,12 +7261,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, logistics-ewm, logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -7654,7 +7656,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-cleancore, integration-deployment</t>
+          <t xml:space="preserve">sales-o2c, ai-readiness, integration-cleancore</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -8564,7 +8566,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-observability, integration-observability</t>
+          <t xml:space="preserve">sales-o2c, ai-readiness, delivery-observability</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -11749,12 +11751,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, integration-deployment, logistics-mdg</t>
+          <t xml:space="preserve">integration-ownership, sales-o2c, integration-deployment</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -12919,7 +12921,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality, ai-readiness, delivery-observability</t>
+          <t xml:space="preserve">logistics-production-quality, sales-o2c, ai-readiness</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -14609,7 +14611,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, delivery-release</t>
+          <t xml:space="preserve">sales-o2c, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -15584,7 +15586,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, sales-o2c, logistics-tm</t>
+          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -18299,7 +18301,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -18309,17 +18311,17 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J222" t="n">
@@ -19744,7 +19746,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -20706,10 +20708,10 @@
         <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -21828,10 +21830,10 @@
         <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -23484,7 +23486,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -23558,7 +23560,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -23595,7 +23597,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -23632,7 +23634,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -23669,7 +23671,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -23706,7 +23708,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, lead-team</t>
+          <t xml:space="preserve">delivery-lifecycle, lead-team, sales-o2c</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -23743,7 +23745,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -23780,7 +23782,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -23817,7 +23819,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -23891,7 +23893,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-ams, delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -23928,7 +23930,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -23965,7 +23967,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -24002,7 +24004,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -24076,7 +24078,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -24113,7 +24115,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -24150,7 +24152,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -24187,7 +24189,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-lifecycle, sales-o2c</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -24251,17 +24253,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales</t>
+          <t xml:space="preserve">SAP Lead Assessment — Start Here</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/sales/</t>
+          <t xml:space="preserve">/labs/assessment/start-here/</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, logistics-ewm, logistics-tm</t>
+          <t xml:space="preserve">ai-readiness, delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -24271,7 +24273,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/start-here/</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -24283,22 +24285,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Business AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment — Start Here</t>
+          <t xml:space="preserve">Business AI Implementation Cases — Business AI Lab</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/start-here/</t>
+          <t xml:space="preserve">/labs/business-ai/cases/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve">ai-readiness, delivery-testing, integration-observability</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -24308,7 +24310,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/start-here/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/cases/</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -24325,17 +24327,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Implementation Cases — Business AI Lab</t>
+          <t xml:space="preserve">Document-to-ERP AI Pilot — From PDF to Controlled Transaction</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/cases/</t>
+          <t xml:space="preserve">/labs/business-ai/document-to-erp-ai/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-testing, integration-observability</t>
+          <t xml:space="preserve">integration-recovery, sales-o2c, ai-readiness</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -24345,7 +24347,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/document-to-erp-ai/</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -24362,17 +24364,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Document-to-ERP AI Pilot — From PDF to Controlled Transaction</t>
+          <t xml:space="preserve">Business AI by Enterprise Domain — Business AI Lab</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/document-to-erp-ai/</t>
+          <t xml:space="preserve">/labs/business-ai/domains/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, sales-o2c, ai-readiness</t>
+          <t xml:space="preserve">sales-o2c, ai-readiness, integration-cleancore</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -24382,7 +24384,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/document-to-erp-ai/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/domains/</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -24399,27 +24401,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI by Enterprise Domain — Business AI Lab</t>
+          <t xml:space="preserve">ERP Agent Gateway Pilot — Safe AI Tool Access to Enterprise Systems</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/domains/</t>
+          <t xml:space="preserve">/labs/business-ai/erp-agent-gateway/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-cleancore, integration-deployment</t>
+          <t xml:space="preserve">ai-agents-mcp, ai-security, ai-data-governance</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/erp-agent-gateway/</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -24436,27 +24438,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERP Agent Gateway Pilot — Safe AI Tool Access to Enterprise Systems</t>
+          <t xml:space="preserve">Business AI Assessment Matrix — Process, Autonomy, Risk, KPI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/erp-agent-gateway/</t>
+          <t xml:space="preserve">/labs/business-ai/matrix/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-security, ai-data-governance</t>
+          <t xml:space="preserve">ai-business-value, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/erp-agent-gateway/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/matrix/</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -24473,17 +24475,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Assessment Matrix — Process, Autonomy, Risk, KPI</t>
+          <t xml:space="preserve">Business AI Graph Model — Business AI Lab</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/matrix/</t>
+          <t xml:space="preserve">/labs/business-ai/model/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-business-value, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -24493,7 +24495,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/matrix/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/model/</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -24510,17 +24512,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Graph Model — Business AI Lab</t>
+          <t xml:space="preserve">Open Enterprise AI Research — ERP Evidence, Safety, and Readiness</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/model/</t>
+          <t xml:space="preserve">/labs/business-ai/open-research/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-data-governance, delivery-testing, ai-evaluation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -24530,7 +24532,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/open-research/</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -24547,17 +24549,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open Enterprise AI Research — ERP Evidence, Safety, and Readiness</t>
+          <t xml:space="preserve">Business AI Patterns — Business AI Lab</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/open-research/</t>
+          <t xml:space="preserve">/labs/business-ai/patterns/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, delivery-testing, ai-evaluation</t>
+          <t xml:space="preserve">integration-deployment, ai-evaluation, ai-readiness</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -24567,7 +24569,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/open-research/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/patterns/</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -24584,17 +24586,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Patterns — Business AI Lab</t>
+          <t xml:space="preserve">Open Enterprise AI Pilots — ERP, Documents, Agents, and Controls</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/patterns/</t>
+          <t xml:space="preserve">/labs/business-ai/pilots/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, ai-evaluation, ai-readiness</t>
+          <t xml:space="preserve">ai-agents-mcp, ai-readiness, ai-data-governance</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -24604,7 +24606,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/patterns/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/pilots/</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -24621,17 +24623,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open Enterprise AI Pilots — ERP, Documents, Agents, and Controls</t>
+          <t xml:space="preserve">Business AI Best Practices and Anti-Patterns</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/pilots/</t>
+          <t xml:space="preserve">/labs/business-ai/practices/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-readiness, ai-data-governance</t>
+          <t xml:space="preserve">ai-readiness, ai-business-value, ai-evaluation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -24641,7 +24643,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/pilots/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/practices/</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -24658,17 +24660,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Best Practices and Anti-Patterns</t>
+          <t xml:space="preserve">Enterprise Processes for Business AI — Business AI Lab</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/practices/</t>
+          <t xml:space="preserve">/labs/business-ai/processes/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, ai-business-value, ai-evaluation</t>
+          <t xml:space="preserve">sales-o2c, ai-readiness, delivery-observability</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -24678,7 +24680,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/practices/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/processes/</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -24695,17 +24697,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Processes for Business AI — Business AI Lab</t>
+          <t xml:space="preserve">Business AI Scenarios — Successes, Mixed Results, Failures</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/processes/</t>
+          <t xml:space="preserve">/labs/business-ai/scenarios/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-observability, integration-observability</t>
+          <t xml:space="preserve">delivery-testing, ai-readiness, delivery-memory</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -24715,7 +24717,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/scenarios/</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -24732,27 +24734,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Scenarios — Successes, Mixed Results, Failures</t>
+          <t xml:space="preserve">Enterprise AI Technology Landscape — Business AI Lab</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/scenarios/</t>
+          <t xml:space="preserve">/labs/business-ai/technologies/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, ai-readiness, delivery-memory</t>
+          <t xml:space="preserve">integration-cleancore, integration-deployment, integration-ownership</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/scenarios/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/technologies/</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -24764,22 +24766,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI</t>
+          <t xml:space="preserve">SAP AIF</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise AI Technology Landscape — Business AI Lab</t>
+          <t xml:space="preserve">Aif</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/technologies/</t>
+          <t xml:space="preserve">/labs/enterprise-context/aif/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, integration-deployment, integration-ownership</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -24789,7 +24791,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/technologies/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/aif/</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -24801,17 +24803,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP AIF</t>
+          <t xml:space="preserve">SAP Automotive JIT/JIS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aif</t>
+          <t xml:space="preserve">Automotive Jit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/aif/</t>
+          <t xml:space="preserve">/labs/enterprise-context/automotive-jit/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -24826,7 +24828,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/aif/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/automotive-jit/</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -24838,32 +24840,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Automotive JIT/JIS</t>
+          <t xml:space="preserve">Business AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automotive Jit</t>
+          <t xml:space="preserve">Agents</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/automotive-jit/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-agents-mcp, delivery-cicd</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/automotive-jit/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -24880,12 +24882,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agents</t>
+          <t xml:space="preserve">Terminology</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/terminology/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -24900,7 +24902,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/terminology/</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -24917,27 +24919,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminology</t>
+          <t xml:space="preserve">SAP Business AI and AI Platform Landscape — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/terminology/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-ai/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, delivery-cicd</t>
+          <t xml:space="preserve">integration-cleancore, ai-agents-mcp, delivery-release</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/terminology/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -24949,32 +24951,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Business AI and AI Platform Landscape — Enterprise Context Lab</t>
+          <t xml:space="preserve">Business Partner</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-ai/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-partner/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, ai-agents-mcp, delivery-release</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-partner/</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -24986,32 +24988,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">Condition Contract Management</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner</t>
+          <t xml:space="preserve">Procurement</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-partner/</t>
+          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/procurement/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-p2p</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-partner/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/procurement/</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -25028,27 +25030,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procurement</t>
+          <t xml:space="preserve">Sales</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/sales/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p</t>
+          <t xml:space="preserve">logistics-ewm, logistics-tm, sales-diagnostics</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/sales/</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -25060,32 +25062,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Condition Contract Management</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales</t>
+          <t xml:space="preserve">Decisions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/aatp-prioritization.html</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-ewm, logistics-tm, sales-diagnostics</t>
+          <t xml:space="preserve">integration-deployment, logistics-mdg, logistics-p2p</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/aatp-prioritization.html</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -25107,7 +25109,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/aatp-prioritization.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -25122,7 +25124,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/aatp-prioritization.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -25134,7 +25136,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -25144,7 +25146,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -25159,7 +25161,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -25171,7 +25173,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -25181,7 +25183,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -25196,7 +25198,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -25218,7 +25220,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -25233,7 +25235,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -25255,7 +25257,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -25270,7 +25272,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -25282,7 +25284,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP EWM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -25292,7 +25294,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -25307,7 +25309,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -25319,7 +25321,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP EWM</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -25329,7 +25331,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/grir-ownership.html</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -25344,7 +25346,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/grir-ownership.html</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -25356,7 +25358,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">Integration Operations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -25366,7 +25368,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/grir-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-api-event.html</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -25381,7 +25383,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/grir-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-api-event.html</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -25403,7 +25405,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-api-event.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -25418,7 +25420,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-api-event.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -25430,7 +25432,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Operations</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -25440,7 +25442,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -25455,7 +25457,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -25467,7 +25469,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -25477,7 +25479,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/master-data-validation.html</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -25492,7 +25494,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/master-data-validation.html</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -25504,7 +25506,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -25514,7 +25516,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/master-data-validation.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -25529,7 +25531,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/master-data-validation.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -25551,7 +25553,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/po-change-impact.html</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -25566,7 +25568,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/po-change-impact.html</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -25578,7 +25580,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -25588,7 +25590,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/po-change-impact.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/pricing-ownership.html</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -25603,7 +25605,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/po-change-impact.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/pricing-ownership.html</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -25615,7 +25617,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -25625,7 +25627,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/pricing-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/retry-idempotency.html</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -25640,7 +25642,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/pricing-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/retry-idempotency.html</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -25662,7 +25664,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/retry-idempotency.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -25677,7 +25679,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/retry-idempotency.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -25699,7 +25701,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/source-selection-ownership.html</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -25714,7 +25716,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/source-selection-ownership.html</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -25736,7 +25738,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/source-selection-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -25751,7 +25753,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/source-selection-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -25773,7 +25775,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -25788,7 +25790,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -25800,7 +25802,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -25810,7 +25812,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/tax-ownership.html</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -25825,7 +25827,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/tax-ownership.html</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -25837,22 +25839,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">ABAP / Extensibility</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decisions</t>
+          <t xml:space="preserve">ABAP Runtime and UI Toolkit — BAL, ALV, SALV and Fiori</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/tax-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, logistics-mdg, logistics-p2p</t>
+          <t xml:space="preserve">integration-development, lead-answer, sales-billing</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -25862,7 +25864,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/tax-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -25879,17 +25881,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABAP Runtime and UI Toolkit — BAL, ALV, SALV and Fiori</t>
+          <t xml:space="preserve">SAP Development Toolbox — Frameworks, Quality and Delivery</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
+          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-development, lead-answer, sales-billing</t>
+          <t xml:space="preserve">ai-data-governance, delivery-cicd, delivery-lifecycle</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -25899,7 +25901,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -25911,22 +25913,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABAP / Extensibility</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Development Toolbox — Frameworks, Quality and Delivery</t>
+          <t xml:space="preserve">Enterprise Business Domains — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/</t>
+          <t xml:space="preserve">/labs/enterprise-context/domains/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, delivery-cicd, delivery-lifecycle</t>
+          <t xml:space="preserve">integration-ownership, sales-o2c, integration-deployment</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -25936,7 +25938,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/domains/</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -25948,22 +25950,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP EWM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Business Domains — Enterprise Context Lab</t>
+          <t xml:space="preserve">Automation</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/domains/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/automation/</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, integration-deployment, logistics-mdg</t>
+          <t xml:space="preserve">ai-data-governance, logistics-ewm</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -25973,7 +25975,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/automation/</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -25990,27 +25992,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automation</t>
+          <t xml:space="preserve">Controls</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/automation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/controls/</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, logistics-ewm</t>
+          <t xml:space="preserve">ai-readiness, logistics-ewm</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/automation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/controls/</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -26027,27 +26029,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Controls</t>
+          <t xml:space="preserve">Domains</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/controls/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/domains/</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, logistics-ewm</t>
+          <t xml:space="preserve">logistics-ewm</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/controls/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/domains/</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -26064,12 +26066,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domains</t>
+          <t xml:space="preserve">Handling Units Packing</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/domains/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/handling-units-packing/</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -26084,7 +26086,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/handling-units-packing/</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -26101,27 +26103,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handling Units Packing</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/handling-units-packing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/integrations/</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-ewm</t>
+          <t xml:space="preserve">integration-patterns, logistics-ewm</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/handling-units-packing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/integrations/</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -26138,17 +26140,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Interfaces</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/interfaces/</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, logistics-ewm</t>
+          <t xml:space="preserve">delivery-testing, logistics-ewm</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -26158,7 +26160,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/interfaces/</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -26175,27 +26177,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interfaces</t>
+          <t xml:space="preserve">Mobility</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/interfaces/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/mobility/</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, logistics-ewm</t>
+          <t xml:space="preserve">logistics-ewm</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/interfaces/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/mobility/</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -26212,12 +26214,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobility</t>
+          <t xml:space="preserve">Objects</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/mobility/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/objects/</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -26232,7 +26234,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/mobility/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/objects/</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -26249,12 +26251,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objects</t>
+          <t xml:space="preserve">Scanners</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/objects/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/scanners/</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -26269,7 +26271,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/objects/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/scanners/</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -26281,22 +26283,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP EWM</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanners</t>
+          <t xml:space="preserve">Finance Logistics</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/scanners/</t>
+          <t xml:space="preserve">/labs/enterprise-context/finance-logistics/</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-ewm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -26306,7 +26308,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/scanners/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/finance-logistics/</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -26318,32 +26320,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finance Logistics</t>
+          <t xml:space="preserve">BRFplus, AIF and ISLM — Decision, Recovery and AI Lifecycle</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/finance-logistics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/frameworks/</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, delivery-cicd, integration-cleancore</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/finance-logistics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/frameworks/</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -26360,17 +26362,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRFplus, AIF and ISLM — Decision, Recovery and AI Lifecycle</t>
+          <t xml:space="preserve">Enterprise Context Lab — Process, Data, Rules and AI Reasoning</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/frameworks/</t>
+          <t xml:space="preserve">/labs/enterprise-context/</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-cicd, integration-cleancore</t>
+          <t xml:space="preserve">integration-ownership, delivery-testing, integration-patterns</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -26380,7 +26382,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/frameworks/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -26397,17 +26399,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Process, Data, Rules and AI Reasoning</t>
+          <t xml:space="preserve">SAP Industry Solutions — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/</t>
+          <t xml:space="preserve">/labs/enterprise-context/industries/</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, delivery-testing, integration-patterns</t>
+          <t xml:space="preserve">logistics-production-quality, sales-o2c, ai-readiness</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -26417,7 +26419,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/industries/</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -26429,22 +26431,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Industry Solutions — Enterprise Context Lab</t>
+          <t xml:space="preserve">Data Migration</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/industries/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/data-migration/</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality, ai-readiness, delivery-observability</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -26454,7 +26456,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/industries/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/data-migration/</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -26466,32 +26468,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Migration</t>
+          <t xml:space="preserve">Iot Devices</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/data-migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/iot-devices/</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/data-migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/iot-devices/</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -26503,32 +26505,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iot Devices</t>
+          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/iot-devices/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/iot-devices/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -26545,17 +26547,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
+          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -26565,7 +26567,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -26582,17 +26584,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
+          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -26602,7 +26604,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -26619,17 +26621,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -26639,7 +26641,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -26656,27 +26658,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
+          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -26688,32 +26690,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
+          <t xml:space="preserve">sales-o2c, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -26725,32 +26727,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, delivery-release</t>
+          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -26767,27 +26769,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
+          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -26804,17 +26806,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -26824,7 +26826,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -26841,17 +26843,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
+          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -26861,7 +26863,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -26878,27 +26880,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -26915,27 +26917,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -26952,17 +26954,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -26972,7 +26974,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -26984,22 +26986,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
+          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -27009,7 +27011,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -27026,17 +27028,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
+          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -27046,7 +27048,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -27058,22 +27060,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, sales-o2c, logistics-tm</t>
+          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -27083,7 +27085,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -27100,17 +27102,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
+          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-master-data</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -27120,7 +27122,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -27137,27 +27139,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-master-data</t>
+          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -27174,27 +27176,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -27211,17 +27213,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
+          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -27231,7 +27233,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -27243,32 +27245,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
+          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
+          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -27280,32 +27282,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
+          <t xml:space="preserve">Anatomy</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -27322,12 +27324,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anatomy</t>
+          <t xml:space="preserve">Casebook</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -27342,7 +27344,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -27359,17 +27361,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casebook</t>
+          <t xml:space="preserve">Configuration</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -27379,7 +27381,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -27396,17 +27398,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuration</t>
+          <t xml:space="preserve">Operations</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
+          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -27416,7 +27418,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -27433,17 +27435,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operations</t>
+          <t xml:space="preserve">Scenarios</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -27453,7 +27455,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -27465,22 +27467,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenarios</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27490,7 +27492,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -27502,32 +27504,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -27539,17 +27541,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27564,7 +27566,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -27581,12 +27583,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27601,7 +27603,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -27618,12 +27620,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27638,7 +27640,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -27655,27 +27657,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -27687,22 +27689,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -27712,7 +27714,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -27724,32 +27726,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -27761,32 +27763,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -27798,17 +27800,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -27823,7 +27825,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -27835,17 +27837,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -27860,7 +27862,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -27872,32 +27874,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -27914,17 +27916,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -27934,7 +27936,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -27946,22 +27948,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -27971,7 +27973,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -27983,32 +27985,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -28020,22 +28022,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28045,7 +28047,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -28062,17 +28064,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28082,7 +28084,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -28099,17 +28101,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28119,7 +28121,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -28136,17 +28138,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28156,7 +28158,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -28173,17 +28175,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -28193,7 +28195,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -28205,32 +28207,32 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -28242,22 +28244,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -28267,7 +28269,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -28276,82 +28278,8 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooling / Roadmap</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/labs/tool-roadmap/</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G159"/>
+  <autoFilter ref="A1:G157"/>
 </worksheet>
 </file>
 

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -177,7 +177,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">38.1%</t>
+          <t xml:space="preserve">38.5%</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,8 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Diagnostics — https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">Sales Diagnostics — https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/
+Sales Analytics &amp; Fulfillment Monitoring — https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -17781,7 +17782,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -17791,7 +17792,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -20642,10 +20643,10 @@
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -27504,17 +27505,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27529,7 +27530,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -27546,12 +27547,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27566,7 +27567,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -27583,12 +27584,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27603,7 +27604,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -27620,27 +27621,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -27652,22 +27653,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27677,7 +27678,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -27689,32 +27690,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -27731,12 +27732,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -27751,7 +27752,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -27763,17 +27764,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -27788,7 +27789,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -27800,17 +27801,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -27825,7 +27826,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -27837,32 +27838,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -27874,32 +27875,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -27911,32 +27912,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -27948,22 +27949,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -27973,7 +27974,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -27990,17 +27991,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28010,7 +28011,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -28027,17 +28028,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28047,7 +28048,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -28064,17 +28065,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28084,7 +28085,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -28101,17 +28102,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28121,7 +28122,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -28138,17 +28139,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28158,7 +28159,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -28170,32 +28171,32 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -28207,32 +28208,32 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -28241,45 +28242,8 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooling / Roadmap</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/labs/tool-roadmap/</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G157"/>
+  <autoFilter ref="A1:G156"/>
 </worksheet>
 </file>
 

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -4017,7 +4017,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-evaluation, ai-retrieval</t>
+          <t xml:space="preserve">ai-agents-mcp, ai-readiness, ai-security</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -22525,7 +22525,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-evaluation, ai-retrieval</t>
+          <t xml:space="preserve">ai-agents-mcp, ai-readiness, ai-security</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">38.5%</t>
+          <t xml:space="preserve">38.7%</t>
         </is>
       </c>
     </row>
@@ -7302,27 +7302,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment — Start Here</t>
+          <t xml:space="preserve">SAP Sales Certification Preparation — C_S4CS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/assessment/start-here/</t>
+          <t xml:space="preserve">/labs/assessment/sales-certification/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/assessment/start-here/index.md</t>
+          <t xml:space="preserve">labs/assessment/sales-certification/index.md</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">excluded</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/start-here/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/sales-certification/</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -7362,42 +7362,42 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Fluency: Early Technical Judgment, Confidence and Tradeoffs</t>
+          <t xml:space="preserve">SAP Lead Assessment — Start Here</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/ai-fluency/</t>
+          <t xml:space="preserve">/labs/assessment/start-here/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/ai-fluency.md</t>
+          <t xml:space="preserve">labs/assessment/start-here/index.md</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-business-value, ai-evaluation, ai-readiness, ai-security</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-readiness, delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-fluency/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/assessment/start-here/</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -7427,22 +7427,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Architecture Patterns — From Reusable Shapes to First-Pass Blueprints</t>
+          <t xml:space="preserve">AI Fluency: Early Technical Judgment, Confidence and Tradeoffs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/architecture-patterns/</t>
+          <t xml:space="preserve">/labs/ai-fluency/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/architecture-patterns.md</t>
+          <t xml:space="preserve">labs/business-ai/ai-fluency.md</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-evaluation, ai-readiness, ai-retrieval, delivery-lifecycle</t>
+          <t xml:space="preserve">ai-business-value, ai-evaluation, ai-readiness, ai-security</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/architecture-patterns/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/ai-fluency/</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -7497,37 +7497,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Implementation Cases — Business AI Lab</t>
+          <t xml:space="preserve">AI Architecture Patterns — From Reusable Shapes to First-Pass Blueprints</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/cases/</t>
+          <t xml:space="preserve">/labs/business-ai/architecture-patterns/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/cases.md</t>
+          <t xml:space="preserve">labs/business-ai/architecture-patterns.md</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-agents-mcp, ai-evaluation, ai-readiness, ai-retrieval, delivery-lifecycle</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-testing, integration-observability</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/architecture-patterns/</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -7562,17 +7562,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Document-to-ERP AI Pilot — From PDF to Controlled Transaction</t>
+          <t xml:space="preserve">Business AI Implementation Cases — Business AI Lab</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/document-to-erp-ai/</t>
+          <t xml:space="preserve">/labs/business-ai/cases/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/document-to-erp-ai.md</t>
+          <t xml:space="preserve">labs/business-ai/cases.md</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, sales-o2c, ai-readiness</t>
+          <t xml:space="preserve">ai-readiness, delivery-testing, integration-observability</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/document-to-erp-ai/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/cases/</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -7627,17 +7627,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI by Enterprise Domain — Business AI Lab</t>
+          <t xml:space="preserve">Document-to-ERP AI Pilot — From PDF to Controlled Transaction</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/domains/</t>
+          <t xml:space="preserve">/labs/business-ai/document-to-erp-ai/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/domains.md</t>
+          <t xml:space="preserve">labs/business-ai/document-to-erp-ai.md</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, ai-readiness, integration-cleancore</t>
+          <t xml:space="preserve">integration-recovery, sales-o2c, ai-readiness</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/document-to-erp-ai/</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -7692,17 +7692,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERP Agent Gateway Pilot — Safe AI Tool Access to Enterprise Systems</t>
+          <t xml:space="preserve">Business AI by Enterprise Domain — Business AI Lab</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/erp-agent-gateway/</t>
+          <t xml:space="preserve">/labs/business-ai/domains/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/erp-agent-gateway.md</t>
+          <t xml:space="preserve">labs/business-ai/domains.md</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-security, ai-data-governance</t>
+          <t xml:space="preserve">sales-o2c, ai-readiness, integration-cleancore</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/erp-agent-gateway/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/domains/</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -7757,42 +7757,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Glossary — Plain Language for Discovery, Architecture, Governance and Delivery</t>
+          <t xml:space="preserve">ERP Agent Gateway Pilot — Safe AI Tool Access to Enterprise Systems</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/glossary/</t>
+          <t xml:space="preserve">/labs/business-ai/erp-agent-gateway/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/glossary.md</t>
+          <t xml:space="preserve">labs/business-ai/erp-agent-gateway.md</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-business-value, ai-evaluation, ai-readiness, ai-security, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-agents-mcp, ai-security, ai-data-governance</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/glossary/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/erp-agent-gateway/</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -7822,17 +7822,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Governance and Data Boundaries — Ownership, Access, Action Risk and Validation</t>
+          <t xml:space="preserve">Business AI Glossary — Plain Language for Discovery, Architecture, Governance and Delivery</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/governance-data-boundaries/</t>
+          <t xml:space="preserve">/labs/business-ai/glossary/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/governance-data-boundaries.md</t>
+          <t xml:space="preserve">labs/business-ai/glossary.md</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, ai-evaluation, ai-readiness, ai-security, delivery-lifecycle</t>
+          <t xml:space="preserve">ai-business-value, ai-evaluation, ai-readiness, ai-security, delivery-lifecycle</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/governance-data-boundaries/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/glossary/</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7882,22 +7882,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">Business AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Implementation Readiness — Evals, Safeguards, Observability, Release and Rollback</t>
+          <t xml:space="preserve">AI Governance and Data Boundaries — Ownership, Access, Action Risk and Validation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/implementation-readiness/</t>
+          <t xml:space="preserve">/labs/business-ai/governance-data-boundaries/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/implementation-readiness.md</t>
+          <t xml:space="preserve">labs/business-ai/governance-data-boundaries.md</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-evaluation, ai-security, delivery-lifecycle</t>
+          <t xml:space="preserve">ai-data-governance, ai-evaluation, ai-readiness, ai-security, delivery-lifecycle</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/implementation-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/governance-data-boundaries/</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7947,22 +7947,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Lab — Processes, Patterns, Technologies, Evidence</t>
+          <t xml:space="preserve">AI Implementation Readiness — Evals, Safeguards, Observability, Release and Rollback</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/</t>
+          <t xml:space="preserve">/labs/business-ai/implementation-readiness/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/index.md</t>
+          <t xml:space="preserve">labs/business-ai/implementation-readiness.md</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-business-value</t>
+          <t xml:space="preserve">ai-evaluation, ai-security, delivery-lifecycle</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/implementation-readiness/</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -8017,22 +8017,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Assessment Matrix — Process, Autonomy, Risk, KPI</t>
+          <t xml:space="preserve">Business AI Lab — Processes, Patterns, Technologies, Evidence</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/matrix/</t>
+          <t xml:space="preserve">/labs/business-ai/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/matrix.md</t>
+          <t xml:space="preserve">labs/business-ai/index.md</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-business-value</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-business-value, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/matrix/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -8082,37 +8082,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Model Selection — Model Classes, Context, Latency, Cost and Evals</t>
+          <t xml:space="preserve">Business AI Assessment Matrix — Process, Autonomy, Risk, KPI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/model-selection/</t>
+          <t xml:space="preserve">/labs/business-ai/matrix/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/model-selection.md</t>
+          <t xml:space="preserve">labs/business-ai/matrix.md</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-business-value, ai-evaluation, ai-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-business-value, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/model-selection/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/matrix/</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -8147,37 +8147,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Graph Model — Business AI Lab</t>
+          <t xml:space="preserve">AI Model Selection — Model Classes, Context, Latency, Cost and Evals</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/model/</t>
+          <t xml:space="preserve">/labs/business-ai/model-selection/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/model.md</t>
+          <t xml:space="preserve">labs/business-ai/model-selection.md</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-business-value, ai-evaluation, ai-readiness</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/model-selection/</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -8212,17 +8212,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open Enterprise AI Research — ERP Evidence, Safety, and Readiness</t>
+          <t xml:space="preserve">Business AI Graph Model — Business AI Lab</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/open-research/</t>
+          <t xml:space="preserve">/labs/business-ai/model/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/open-research.md</t>
+          <t xml:space="preserve">labs/business-ai/model.md</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, delivery-testing, ai-evaluation</t>
+          <t xml:space="preserve">ai-readiness, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/open-research/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/model/</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -8277,17 +8277,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Patterns — Business AI Lab</t>
+          <t xml:space="preserve">Open Enterprise AI Research — ERP Evidence, Safety, and Readiness</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/patterns/</t>
+          <t xml:space="preserve">/labs/business-ai/open-research/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/patterns.md</t>
+          <t xml:space="preserve">labs/business-ai/open-research.md</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, ai-evaluation, ai-readiness</t>
+          <t xml:space="preserve">ai-data-governance, delivery-testing, ai-evaluation</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/patterns/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/open-research/</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -8342,17 +8342,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open Enterprise AI Pilots — ERP, Documents, Agents, and Controls</t>
+          <t xml:space="preserve">Business AI Patterns — Business AI Lab</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/pilots/</t>
+          <t xml:space="preserve">/labs/business-ai/patterns/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/pilots.md</t>
+          <t xml:space="preserve">labs/business-ai/patterns.md</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-readiness, ai-data-governance</t>
+          <t xml:space="preserve">integration-deployment, ai-evaluation, ai-readiness</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/pilots/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/patterns/</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8407,37 +8407,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Platform Building Blocks — Capability Roles, Minimum Set and Control Boundaries</t>
+          <t xml:space="preserve">Open Enterprise AI Pilots — ERP, Documents, Agents, and Controls</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/platform-building-blocks/</t>
+          <t xml:space="preserve">/labs/business-ai/pilots/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/platform-building-blocks.md</t>
+          <t xml:space="preserve">labs/business-ai/pilots.md</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-evaluation, ai-readiness, ai-retrieval, ai-security</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-agents-mcp, ai-readiness, ai-data-governance</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/platform-building-blocks/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/pilots/</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8472,37 +8472,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Best Practices and Anti-Patterns</t>
+          <t xml:space="preserve">AI Platform Building Blocks — Capability Roles, Minimum Set and Control Boundaries</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/practices/</t>
+          <t xml:space="preserve">/labs/business-ai/platform-building-blocks/</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/practices.md</t>
+          <t xml:space="preserve">labs/business-ai/platform-building-blocks.md</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-agents-mcp, ai-evaluation, ai-readiness, ai-retrieval, ai-security</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, ai-business-value, ai-evaluation</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/practices/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/platform-building-blocks/</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8537,17 +8537,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Processes for Business AI — Business AI Lab</t>
+          <t xml:space="preserve">Business AI Best Practices and Anti-Patterns</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/processes/</t>
+          <t xml:space="preserve">/labs/business-ai/practices/</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/processes.md</t>
+          <t xml:space="preserve">labs/business-ai/practices.md</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, ai-readiness, delivery-observability</t>
+          <t xml:space="preserve">ai-readiness, ai-business-value, ai-evaluation</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/practices/</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8602,37 +8602,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Solution Routing — From Customer Label to OpenAI Path</t>
+          <t xml:space="preserve">Enterprise Processes for Business AI — Business AI Lab</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/routing/</t>
+          <t xml:space="preserve">/labs/business-ai/processes/</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/routing.md</t>
+          <t xml:space="preserve">labs/business-ai/processes.md</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-readiness, integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, ai-readiness, delivery-observability</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/routing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/processes/</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8667,37 +8667,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Scenarios — Successes, Mixed Results, Failures</t>
+          <t xml:space="preserve">Business AI Solution Routing — From Customer Label to OpenAI Path</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/scenarios/</t>
+          <t xml:space="preserve">/labs/business-ai/routing/</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/scenarios.md</t>
+          <t xml:space="preserve">labs/business-ai/routing.md</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-agents-mcp, ai-readiness, integration-patterns</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, ai-readiness, delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/scenarios/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/routing/</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8732,17 +8732,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise AI Technology Landscape — Business AI Lab</t>
+          <t xml:space="preserve">Business AI Scenarios — Successes, Mixed Results, Failures</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/technologies/</t>
+          <t xml:space="preserve">/labs/business-ai/scenarios/</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/technologies.md</t>
+          <t xml:space="preserve">labs/business-ai/scenarios.md</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, integration-deployment, integration-ownership</t>
+          <t xml:space="preserve">delivery-testing, ai-readiness, delivery-memory</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/technologies/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/scenarios/</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8797,42 +8797,42 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI Vertical Context — Adapt the Route to the Operating Reality</t>
+          <t xml:space="preserve">Enterprise AI Technology Landscape — Business AI Lab</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/business-ai/vertical-context/</t>
+          <t xml:space="preserve">/labs/business-ai/technologies/</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/business-ai/vertical-context.md</t>
+          <t xml:space="preserve">labs/business-ai/technologies.md</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-business-value, ai-readiness, integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-cleancore, integration-deployment, integration-ownership</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/vertical-context/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/technologies/</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8857,22 +8857,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Assurance</t>
+          <t xml:space="preserve">Business AI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Certification Catalog — What Each Certificate Actually Proves</t>
+          <t xml:space="preserve">Business AI Vertical Context — Adapt the Route to the Operating Reality</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-assurance/certification-catalog/</t>
+          <t xml:space="preserve">/labs/business-ai/vertical-context/</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-assurance/certification-catalog/index.md</t>
+          <t xml:space="preserve">labs/business-ai/vertical-context.md</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, lead-decision, lead-evidence, logistics-production-quality</t>
+          <t xml:space="preserve">ai-business-value, ai-readiness, integration-patterns</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/certification-catalog/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/business-ai/vertical-context/</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8927,17 +8927,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cloud and Industry Assurance — Enterprise Assurance</t>
+          <t xml:space="preserve">Enterprise Certification Catalog — What Each Certificate Actually Proves</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-assurance/cloud-industry-assurance/</t>
+          <t xml:space="preserve">/labs/enterprise-assurance/certification-catalog/</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-assurance/cloud-industry-assurance/index.md</t>
+          <t xml:space="preserve">labs/enterprise-assurance/certification-catalog/index.md</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-security, integration-deployment, lead-evidence</t>
+          <t xml:space="preserve">integration-deployment, lead-decision, lead-evidence, logistics-production-quality</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/cloud-industry-assurance/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/certification-catalog/</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8992,17 +8992,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Assurance — Certifications, Reports and Vendor Evidence</t>
+          <t xml:space="preserve">Cloud and Industry Assurance — Enterprise Assurance</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-assurance/</t>
+          <t xml:space="preserve">/labs/enterprise-assurance/cloud-industry-assurance/</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-assurance/index.md</t>
+          <t xml:space="preserve">labs/enterprise-assurance/cloud-industry-assurance/index.md</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">ai-security, integration-deployment, lead-evidence</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/cloud-industry-assurance/</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9057,17 +9057,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISO Management Systems — Enterprise Assurance</t>
+          <t xml:space="preserve">Enterprise Assurance — Certifications, Reports and Vendor Evidence</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-assurance/iso-management-systems/</t>
+          <t xml:space="preserve">/labs/enterprise-assurance/</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-assurance/iso-management-systems/index.md</t>
+          <t xml:space="preserve">labs/enterprise-assurance/index.md</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-security, delivery-lifecycle, lead-evidence</t>
+          <t xml:space="preserve">integration-deployment, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/iso-management-systems/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9122,17 +9122,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISAE 3402 and SOC Reports — Enterprise Assurance</t>
+          <t xml:space="preserve">ISO Management Systems — Enterprise Assurance</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-assurance/service-organization-reports/</t>
+          <t xml:space="preserve">/labs/enterprise-assurance/iso-management-systems/</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-assurance/service-organization-reports/index.md</t>
+          <t xml:space="preserve">labs/enterprise-assurance/iso-management-systems/index.md</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, integration-ownership, lead-evidence</t>
+          <t xml:space="preserve">ai-security, delivery-lifecycle, lead-evidence</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/service-organization-reports/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/iso-management-systems/</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9187,17 +9187,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendor Due Diligence — Enterprise Assurance</t>
+          <t xml:space="preserve">ISAE 3402 and SOC Reports — Enterprise Assurance</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-assurance/vendor-due-diligence/</t>
+          <t xml:space="preserve">/labs/enterprise-assurance/service-organization-reports/</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-assurance/vendor-due-diligence/index.md</t>
+          <t xml:space="preserve">labs/enterprise-assurance/service-organization-reports/index.md</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">integration-deployment, integration-ownership, lead-evidence</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/vendor-due-diligence/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/service-organization-reports/</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9247,37 +9247,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP AIF</t>
+          <t xml:space="preserve">Enterprise Assurance</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aif</t>
+          <t xml:space="preserve">Vendor Due Diligence — Enterprise Assurance</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/aif/</t>
+          <t xml:space="preserve">/labs/enterprise-assurance/vendor-due-diligence/</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/aif/index.html</t>
+          <t xml:space="preserve">labs/enterprise-assurance/vendor-due-diligence/index.md</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/aif/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-assurance/vendor-due-diligence/</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9312,27 +9312,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP aATP / ATP</t>
+          <t xml:space="preserve">SAP AIF</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atp</t>
+          <t xml:space="preserve">Aif</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/atp/</t>
+          <t xml:space="preserve">/labs/enterprise-context/aif/</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/atp/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/aif/index.html</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-atp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/atp/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/aif/</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9377,27 +9377,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Automotive JIT/JIS</t>
+          <t xml:space="preserve">SAP aATP / ATP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automotive Jit</t>
+          <t xml:space="preserve">Atp</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/automotive-jit/</t>
+          <t xml:space="preserve">/labs/enterprise-context/atp/</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/automotive-jit/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/atp/index.html</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-atp</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/automotive-jit/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/atp/</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9442,27 +9442,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Billing</t>
+          <t xml:space="preserve">SAP Automotive JIT/JIS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billing</t>
+          <t xml:space="preserve">Automotive Jit</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/billing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/automotive-jit/</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/billing/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/automotive-jit/index.html</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-billing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/billing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/automotive-jit/</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9507,27 +9507,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business AI</t>
+          <t xml:space="preserve">SAP Billing</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agents</t>
+          <t xml:space="preserve">Billing</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/</t>
+          <t xml:space="preserve">/labs/enterprise-context/billing/</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/business-ai/agents/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/billing/index.html</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9537,17 +9537,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-billing</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, delivery-cicd</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/billing/</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9577,17 +9577,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminology</t>
+          <t xml:space="preserve">Agents</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/terminology/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/business-ai/agents/terminology/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/business-ai/agents/index.html</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/terminology/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9642,17 +9642,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Business AI and AI Platform Landscape — Enterprise Context Lab</t>
+          <t xml:space="preserve">Terminology</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-ai/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-ai/agents/terminology/</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/business-ai/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/business-ai/agents/terminology/index.html</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, ai-agents-mcp, delivery-release</t>
+          <t xml:space="preserve">ai-agents-mcp, delivery-cicd</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/agents/terminology/</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9702,22 +9702,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">Business AI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner</t>
+          <t xml:space="preserve">SAP Business AI and AI Platform Landscape — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/business-partner/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-ai/</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/business-partner/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/business-ai/index.md</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-cleancore, ai-agents-mcp, delivery-release</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-partner/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-ai/</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9767,27 +9767,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Condition Contract Management</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Condition Contract Management</t>
+          <t xml:space="preserve">Business Partner</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/business-partner/</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/condition-contract-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/business-partner/index.html</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, sales-pricing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/business-partner/</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9837,22 +9837,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procurement</t>
+          <t xml:space="preserve">Condition Contract Management</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/condition-contract-management/procurement/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/condition-contract-management/index.html</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-p2p, sales-pricing</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9902,17 +9902,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales</t>
+          <t xml:space="preserve">Procurement</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/procurement/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/condition-contract-management/sales/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/condition-contract-management/procurement/index.html</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9932,12 +9932,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-ewm, logistics-tm, sales-diagnostics</t>
+          <t xml:space="preserve">logistics-p2p</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/procurement/</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9962,27 +9962,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Credit Management</t>
+          <t xml:space="preserve">Condition Contract Management</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit</t>
+          <t xml:space="preserve">Sales</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/credit/</t>
+          <t xml:space="preserve">/labs/enterprise-context/condition-contract-management/sales/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/credit/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/condition-contract-management/sales/index.html</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-credit</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-ewm, logistics-tm, sales-diagnostics</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/credit/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/sales/</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10027,22 +10027,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Governance</t>
+          <t xml:space="preserve">SAP Credit Management</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data, Master Data and Governance — Enterprise Context Lab</t>
+          <t xml:space="preserve">Credit</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/data-governance/</t>
+          <t xml:space="preserve">/labs/enterprise-context/credit/</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/data-governance/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/credit/index.html</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, logistics-mdg</t>
+          <t xml:space="preserve">sales-credit</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/data-governance/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/credit/</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10092,27 +10092,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">Data Governance</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decisions</t>
+          <t xml:space="preserve">Data, Master Data and Governance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/aatp-prioritization.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/data-governance/</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/aatp-prioritization.html</t>
+          <t xml:space="preserve">labs/enterprise-context/data-governance/index.md</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10122,17 +10122,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-data-governance, logistics-mdg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, logistics-mdg, logistics-p2p</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/aatp-prioritization.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/data-governance/</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/aatp-prioritization.html</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/account-assignment-ownership.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/aatp-prioritization.html</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/aatp-prioritization.html</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10222,7 +10222,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10232,12 +10232,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/account-assignment-ownership.html</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/account-assignment-ownership.html</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10287,7 +10287,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10297,12 +10297,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ai-logistics-boundary.html</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/clean-core-extension-placement.html</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/delivery-block-ownership.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/confirmed-date-ownership.html</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10482,7 +10482,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP EWM</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10492,12 +10492,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/delivery-block-ownership.html</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/delivery-block-ownership.html</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10547,7 +10547,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP EWM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/grir-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/grir-ownership.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/grir-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ewm-execution-ownership.html</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Operations</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10622,12 +10622,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-api-event.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/grir-ownership.html</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/idoc-api-event.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/grir-ownership.html</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-api-event.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/grir-ownership.html</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10687,12 +10687,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-api-event.html</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/idoc-api-event.html</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-api-event.html</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10742,7 +10742,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">Integration Operations</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/idoc-failure-ownership.html</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10817,12 +10817,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/master-data-validation.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/master-data-validation.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/index.html</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/master-data-validation.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -10872,7 +10872,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/master-data-validation.html</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/master-data-validation.html</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/master-data-validation.html</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/po-change-impact.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/po-change-impact.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/po-change-impact.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/ordering-sequence-guarantees.html</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -11002,7 +11002,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/pricing-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/po-change-impact.html</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/pricing-ownership.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/po-change-impact.html</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/pricing-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/po-change-impact.html</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -11067,7 +11067,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/retry-idempotency.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/pricing-ownership.html</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/retry-idempotency.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/pricing-ownership.html</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/retry-idempotency.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/pricing-ownership.html</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/retry-idempotency.html</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/retry-idempotency.html</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/retry-idempotency.html</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -11207,12 +11207,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/source-selection-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/source-selection-ownership.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/source-selection-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sales-item-behavior-ownership.html</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/source-selection-ownership.html</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/source-selection-ownership.html</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/source-selection-ownership.html</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/sto-vs-intercompany.html</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11392,7 +11392,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11402,12 +11402,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/decisions/tax-ownership.html</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/decisions/tax-ownership.html</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/tax-ownership.html</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/subcontracting-vs-standard-procurement.html</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11457,27 +11457,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">S/4HANA Deployment Models</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Deployment Models — Enterprise Context Lab</t>
+          <t xml:space="preserve">Decisions</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/deployment-models/</t>
+          <t xml:space="preserve">/labs/enterprise-context/decisions/tax-ownership.html</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/deployment-models/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/decisions/tax-ownership.html</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -11487,17 +11487,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-deployment, logistics-mdg, logistics-p2p</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/deployment-models/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/decisions/tax-ownership.html</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11522,22 +11522,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABAP / Extensibility</t>
+          <t xml:space="preserve">S/4HANA Deployment Models</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Development Architecture — RAP, CAP, ABAP Cloud and Clean Core</t>
+          <t xml:space="preserve">SAP S/4HANA Deployment Models — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/development/</t>
+          <t xml:space="preserve">/labs/enterprise-context/deployment-models/</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/development/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/deployment-models/index.md</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-development</t>
+          <t xml:space="preserve">integration-deployment</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/deployment-models/</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11592,22 +11592,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABAP Runtime and UI Toolkit — BAL, ALV, SALV and Fiori</t>
+          <t xml:space="preserve">SAP Development Architecture — RAP, CAP, ABAP Cloud and Clean Core</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
+          <t xml:space="preserve">/labs/enterprise-context/development/</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/development/toolbox/abap-runtime-ui/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/development/index.md</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -11617,12 +11617,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-development</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-development, lead-answer, sales-billing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11657,17 +11657,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Development Toolbox — Frameworks, Quality and Delivery</t>
+          <t xml:space="preserve">ABAP Runtime and UI Toolkit — BAL, ALV, SALV and Fiori</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/</t>
+          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/development/toolbox/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/development/toolbox/abap-runtime-ui/index.md</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, delivery-cicd, delivery-lifecycle</t>
+          <t xml:space="preserve">integration-development, lead-answer, sales-billing</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/abap-runtime-ui/</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11717,22 +11717,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">ABAP / Extensibility</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Business Domains — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP Development Toolbox — Frameworks, Quality and Delivery</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/domains/</t>
+          <t xml:space="preserve">/labs/enterprise-context/development/toolbox/</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/domains/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/development/toolbox/index.md</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, sales-o2c, integration-deployment</t>
+          <t xml:space="preserve">ai-data-governance, delivery-cicd, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/development/toolbox/</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11782,27 +11782,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">End To End Analytics</t>
+          <t xml:space="preserve">Enterprise Business Domains — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/end-to-end-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/domains/</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/end-to-end-analytics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/domains/index.md</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -11812,17 +11812,17 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-observability, integration-observability</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, sales-o2c, integration-deployment</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/end-to-end-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/domains/</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11847,27 +11847,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP EWM</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automation</t>
+          <t xml:space="preserve">End To End Analytics</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/automation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/end-to-end-analytics/</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/ewm/automation/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/end-to-end-analytics/index.html</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -11877,12 +11877,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-observability, integration-observability</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, logistics-ewm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/automation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/end-to-end-analytics/</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11917,17 +11917,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Controls</t>
+          <t xml:space="preserve">Automation</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/controls/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/automation/</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/ewm/controls/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/ewm/automation/index.html</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, logistics-ewm</t>
+          <t xml:space="preserve">ai-data-governance, logistics-ewm</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/controls/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/automation/</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domains</t>
+          <t xml:space="preserve">Controls</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/domains/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/controls/</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/ewm/domains/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/ewm/controls/index.html</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12012,12 +12012,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-ewm</t>
+          <t xml:space="preserve">ai-readiness, logistics-ewm</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/controls/</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12047,17 +12047,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handling Units Packing</t>
+          <t xml:space="preserve">Domains</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/handling-units-packing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/domains/</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/ewm/handling-units-packing/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/ewm/domains/index.html</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/handling-units-packing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/domains/</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12112,22 +12112,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ewm</t>
+          <t xml:space="preserve">Handling Units Packing</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/handling-units-packing/</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/ewm/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/ewm/handling-units-packing/index.html</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -12137,14 +12137,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
           <t xml:space="preserve">logistics-ewm</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I127" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/handling-units-packing/</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12177,22 +12177,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Ewm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/ewm/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/ewm/index.html</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -12202,17 +12202,17 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-ewm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, logistics-ewm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12242,17 +12242,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interfaces</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/interfaces/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/integrations/</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/ewm/interfaces/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/ewm/integrations/index.html</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, logistics-ewm</t>
+          <t xml:space="preserve">integration-patterns, logistics-ewm</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/interfaces/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/integrations/</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12307,17 +12307,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobility</t>
+          <t xml:space="preserve">Interfaces</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/mobility/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/interfaces/</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/ewm/mobility/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/ewm/interfaces/index.html</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12337,12 +12337,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-ewm</t>
+          <t xml:space="preserve">delivery-testing, logistics-ewm</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/mobility/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/interfaces/</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12372,17 +12372,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objects</t>
+          <t xml:space="preserve">Mobility</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/objects/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/mobility/</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/ewm/objects/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/ewm/mobility/index.html</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/objects/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/mobility/</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -12437,17 +12437,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanners</t>
+          <t xml:space="preserve">Objects</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/ewm/scanners/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/objects/</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/ewm/scanners/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/ewm/objects/index.html</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/scanners/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/objects/</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12497,47 +12497,47 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP EWM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Experience Platforms — Enterprise Context Lab</t>
+          <t xml:space="preserve">Scanners</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/experience-platforms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/ewm/scanners/</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/experience-platforms/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/ewm/scanners/index.html</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-ewm</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/experience-platforms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/ewm/scanners/</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12567,17 +12567,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Build Work Zone — Enterprise Context Lab</t>
+          <t xml:space="preserve">Experience Platforms — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/experience-platforms/sap-build-work-zone/</t>
+          <t xml:space="preserve">/labs/enterprise-context/experience-platforms/</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/experience-platforms/sap-build-work-zone/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/experience-platforms/index.md</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, integration-patterns, lead-decision</t>
+          <t xml:space="preserve">integration-ownership, integration-patterns</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/experience-platforms/sap-build-work-zone/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/experience-platforms/</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -12627,37 +12627,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finance Logistics</t>
+          <t xml:space="preserve">SAP Build Work Zone — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/finance-logistics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/experience-platforms/sap-build-work-zone/</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/finance-logistics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/experience-platforms/sap-build-work-zone/index.md</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, integration-patterns, lead-decision</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/finance-logistics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/experience-platforms/sap-build-work-zone/</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -12697,32 +12697,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Payments, Banks and Rejections — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Finance Logistics</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/finance-logistics/payments-banks-rejections/</t>
+          <t xml:space="preserve">/labs/enterprise-context/finance-logistics/</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/finance-logistics/payments-banks-rejections/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/finance-logistics/index.html</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, sales-diagnostics, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/finance-logistics/payments-banks-rejections/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/finance-logistics/</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -12757,42 +12757,42 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRFplus, AIF and ISLM — Decision, Recovery and AI Lifecycle</t>
+          <t xml:space="preserve">Payments, Banks and Rejections — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/frameworks/</t>
+          <t xml:space="preserve">/labs/enterprise-context/finance-logistics/payments-banks-rejections/</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/frameworks/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/finance-logistics/payments-banks-rejections/index.md</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, sales-diagnostics, sales-o2c</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-cicd, integration-cleancore</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/frameworks/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/finance-logistics/payments-banks-rejections/</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -12827,17 +12827,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Process, Data, Rules and AI Reasoning</t>
+          <t xml:space="preserve">BRFplus, AIF and ISLM — Decision, Recovery and AI Lifecycle</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/</t>
+          <t xml:space="preserve">/labs/enterprise-context/frameworks/</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/frameworks/index.md</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, delivery-testing, integration-patterns</t>
+          <t xml:space="preserve">delivery-ams, delivery-cicd, integration-cleancore</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/frameworks/</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -12892,17 +12892,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Industry Solutions — Enterprise Context Lab</t>
+          <t xml:space="preserve">Enterprise Context Lab — Process, Data, Rules and AI Reasoning</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/industries/</t>
+          <t xml:space="preserve">/labs/enterprise-context/</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/industries/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/index.md</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality, sales-o2c, ai-readiness</t>
+          <t xml:space="preserve">integration-ownership, delivery-testing, integration-patterns</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12940,7 +12940,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/industries/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -12952,27 +12952,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Operations</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Operations</t>
+          <t xml:space="preserve">SAP Industry Solutions — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integration-operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/industries/</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integration-operations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/industries/index.md</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -12982,12 +12982,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality, sales-o2c, ai-readiness</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integration-operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/industries/</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13017,22 +13017,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">Integration Operations</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Business Partner API — Data Model, Segments, CVI and Integration Design</t>
+          <t xml:space="preserve">Integration Operations</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/business-partner-api/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integration-operations/</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integrations/business-partner-api/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/integration-operations/index.html</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -13042,12 +13042,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/business-partner-api/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integration-operations/</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13082,42 +13082,42 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Migration</t>
+          <t xml:space="preserve">SAP Business Partner API — Data Model, Segments, CVI and Integration Design</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/data-migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/business-partner-api/</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integrations/data-migration/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/business-partner-api/index.md</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/data-migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/business-partner-api/</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13152,37 +13152,37 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP DRF — Data Replication Framework</t>
+          <t xml:space="preserve">Data Migration</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/drf/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/data-migration/</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integrations/drf/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/data-migration/index.html</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/drf/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/data-migration/</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13217,17 +13217,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Integration Architecture — Logistics, Events and Data Distribution</t>
+          <t xml:space="preserve">SAP DRF — Data Replication Framework</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/drf/</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integrations/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/drf/index.md</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13237,12 +13237,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/drf/</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13277,22 +13277,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Inventory Management</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inventory Management</t>
+          <t xml:space="preserve">SAP Integration Architecture — Logistics, Events and Data Distribution</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/inventory-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/inventory-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/index.md</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-inventory</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/inventory-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13342,27 +13342,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Inventory Management</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iot Devices</t>
+          <t xml:space="preserve">Inventory Management</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/iot-devices/</t>
+          <t xml:space="preserve">/labs/enterprise-context/inventory-management/</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/iot-devices/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/inventory-management/index.html</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-inventory</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/iot-devices/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/inventory-management/</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13407,27 +13407,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Kanban</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Cycle</t>
+          <t xml:space="preserve">Iot Devices</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/control-cycle/</t>
+          <t xml:space="preserve">/labs/enterprise-context/iot-devices/</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/control-cycle/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/iot-devices/index.html</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/control-cycle/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/iot-devices/</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -13477,17 +13477,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kanban</t>
+          <t xml:space="preserve">Control Cycle</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/control-cycle/</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/control-cycle/index.html</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/control-cycle/</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -13542,17 +13542,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operations Diagnostics</t>
+          <t xml:space="preserve">Kanban</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/operations-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/operations-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/index.html</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-inventory</t>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/operations-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -13607,17 +13607,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull Control</t>
+          <t xml:space="preserve">Operations Diagnostics</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/pull-control/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/operations-diagnostics/</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/pull-control/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/operations-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">logistics-inventory</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/pull-control/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/operations-diagnostics/</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -13672,17 +13672,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Replenishment Strategies</t>
+          <t xml:space="preserve">Pull Control</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/replenishment-strategies/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/pull-control/</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/replenishment-strategies/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/pull-control/index.html</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p</t>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/replenishment-strategies/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/pull-control/</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Runtime Flows</t>
+          <t xml:space="preserve">Replenishment Strategies</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/runtime-flows/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/replenishment-strategies/</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/runtime-flows/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/replenishment-strategies/index.html</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/runtime-flows/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/replenishment-strategies/</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -13802,17 +13802,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statuses Signals</t>
+          <t xml:space="preserve">Runtime Flows</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/statuses-signals/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/runtime-flows/</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/statuses-signals/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/runtime-flows/index.html</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-inventory</t>
+          <t xml:space="preserve">logistics-p2p</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/statuses-signals/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/runtime-flows/</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -13862,22 +13862,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP Kanban</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logistics Capabilities</t>
+          <t xml:space="preserve">Statuses Signals</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/logistics-capabilities/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/statuses-signals/</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/logistics-capabilities/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/statuses-signals/index.html</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership</t>
+          <t xml:space="preserve">logistics-inventory</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/logistics-capabilities/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/statuses-signals/</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -13927,22 +13927,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Logistics Capabilities</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/logistics-capabilities/</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/logistics-capabilities/index.html</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data</t>
+          <t xml:space="preserve">integration-ownership</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/logistics-capabilities/</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -13997,17 +13997,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material Behavior</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/material-behavior/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/material-behavior/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/index.html</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/material-behavior/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14057,27 +14057,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
+          <t xml:space="preserve">Material Behavior</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">/labs/enterprise-context/material-behavior/</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/architecture/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/material-behavior/index.html</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -14087,12 +14087,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/material-behavior/</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -14127,37 +14127,37 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lead Assessment Drills — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/assessment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/assessment/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/architecture/index.md</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, lead-decision, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/assessment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -14192,37 +14192,37 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Lead Assessment Drills — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/assessment/</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/build-runtime/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/assessment/index.md</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, lead-decision, logistics-mdg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/assessment/</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -14257,37 +14257,37 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Consolidation &amp; Golden Record — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/build-runtime/index.md</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -14322,17 +14322,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Matching &amp; Survivorship — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Consolidation &amp; Golden Record — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/survivorship/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/survivorship/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/index.md</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/survivorship/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -14387,37 +14387,37 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Matching &amp; Survivorship — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/survivorship/</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/engineering/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/survivorship/index.md</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/survivorship/</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -14452,17 +14452,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/engineering/index.md</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
+          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -14517,17 +14517,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/deployments/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/index.md</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -14577,22 +14577,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/entity-map/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/deployments/index.md</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14612,12 +14612,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, integration-observability, integration-recovery</t>
+          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -14647,37 +14647,37 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner, Customer &amp; Supplier — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/entity-map/index.md</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -14707,22 +14707,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Domain Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Business Partner, Customer &amp; Supplier — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/index.md</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg, sales-o2c</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -14777,42 +14777,42 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Domain Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/entity-map/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/index.md</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -14842,42 +14842,42 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Domain — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/entity-map/index.md</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -14907,37 +14907,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Material Domain — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/extensions/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/index.md</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -14972,17 +14972,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/brfplus-rules/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/extensions/index.md</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -15037,37 +15037,37 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Change Request Type Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/change-request-matrix/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/brfplus-rules/index.md</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-decision, logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -15102,17 +15102,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Engine — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Change Request Type Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/change-request-matrix/index.md</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -15167,37 +15167,37 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Governance Engine — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/impact/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/index.md</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-decision, logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -15232,17 +15232,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
+          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/implementation/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/impact/index.md</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -15262,12 +15262,12 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
+          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15292,27 +15292,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Governance</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data Governance — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/implementation/index.md</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -15322,17 +15322,17 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J176" t="n">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15357,27 +15357,27 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Data Governance</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP Master Data Governance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/interfaces/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/index.md</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -15387,17 +15387,17 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -15427,17 +15427,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/lineage/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/interfaces/index.md</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -15457,7 +15457,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -15487,22 +15487,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/cases/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/lineage/index.md</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
+          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -15557,17 +15557,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/cases/index.md</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
+          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -15617,22 +15617,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/migration/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/index.md</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -15687,17 +15687,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/ownership/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/migration/index.md</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-master-data</t>
+          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
+          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/processes/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/ownership/index.md</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -15782,12 +15782,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
+          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-master-data</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -15817,17 +15817,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/reasoning/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/processes/index.md</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -15847,12 +15847,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
+          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -15865,7 +15865,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -15882,37 +15882,37 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Replication &amp; Distribution — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/replication/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/reasoning/index.md</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -15947,17 +15947,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG DRF Operations &amp; Replay — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Replication &amp; Distribution — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/replication/operations/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/replication/index.md</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -16012,37 +16012,37 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG DRF Operations &amp; Replay — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/operations/</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/scenario/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/replication/operations/index.md</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/operations/</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -16072,42 +16072,42 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA API-Led Migration — Design, Restart and Cutover</t>
+          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/api-led-migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/api-led-migration.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/scenario/index.md</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-patterns, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/api-led-migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -16142,17 +16142,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Cutover — Rehearsal, Delta and Reconciliation</t>
+          <t xml:space="preserve">SAP S/4HANA API-Led Migration — Design, Restart and Cutover</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/cutover/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/api-led-migration/</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/cutover.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/api-led-migration.md</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-recovery, logistics-inventory</t>
+          <t xml:space="preserve">delivery-release, integration-patterns, integration-recovery</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/cutover/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/api-led-migration/</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -16207,17 +16207,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Design Register — Object Control</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Cutover — Rehearsal, Delta and Reconciliation</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/design-register/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/cutover/</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/design-register.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/cutover.md</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
+          <t xml:space="preserve">delivery-release, integration-recovery, logistics-inventory</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/design-register/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/cutover/</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -16272,17 +16272,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Domain Playbooks — SD, MM, PP, EWM, FI and CO</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Design Register — Object Control</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/domain-playbooks/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/design-register/</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/domain-playbooks.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/design-register.md</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -16297,7 +16297,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, logistics-production-quality, sales-o2c</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/domain-playbooks/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/design-register/</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -16337,17 +16337,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Greenfield Migration — Architecture and Data Load</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Domain Playbooks — SD, MM, PP, EWM, FI and CO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/domain-playbooks/</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/domain-playbooks.md</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, logistics-master-data</t>
+          <t xml:space="preserve">logistics-p2p, logistics-production-quality, sales-o2c</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/domain-playbooks/</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -16402,17 +16402,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Lead Assessment — Architecture Drills</t>
+          <t xml:space="preserve">SAP S/4HANA Greenfield Migration — Architecture and Data Load</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/lead-assessment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/lead-assessment.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/index.md</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, logistics-master-data</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/lead-assessment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -16467,17 +16467,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Factory — Governance, Mock Cycles and Ownership</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Lead Assessment — Architecture Drills</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/migration-factory/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/lead-assessment/</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/migration-factory.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/lead-assessment.md</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-recovery, lead-decision</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -16515,7 +16515,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/migration-factory/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/lead-assessment/</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -16532,17 +16532,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Object Catalog — Greenfield Load Scope</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Factory — Governance, Mock Cycles and Ownership</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/object-catalog/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/migration-factory/</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/object-catalog.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/migration-factory.md</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-release, integration-recovery, lead-decision</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/object-catalog/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/migration-factory/</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -16597,17 +16597,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Tools — Cockpit, APIs and Integration</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Object Catalog — Greenfield Load Scope</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/tooling/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/object-catalog/</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/tooling.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/object-catalog.md</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, integration-deployment, integration-patterns</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/tooling/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/object-catalog/</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -16657,47 +16657,47 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Tools — Cockpit, APIs and Integration</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/tooling/</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/model/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/tooling.md</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-cicd, integration-deployment, integration-patterns</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J197" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/tooling/</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -16722,47 +16722,47 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Performance</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Performance and Technical Operations — Practical S/4HANA Troubleshooting</t>
+          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/performance/</t>
+          <t xml:space="preserve">/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/performance/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/model/index.md</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-observability, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J198" t="n">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/performance/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -16787,42 +16787,42 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP Performance</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anatomy</t>
+          <t xml:space="preserve">SAP Performance and Technical Operations — Practical S/4HANA Troubleshooting</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">/labs/enterprise-context/performance/</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/anatomy/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/performance/index.md</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-observability, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/performance/</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -16857,17 +16857,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casebook</t>
+          <t xml:space="preserve">Anatomy</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/casebook/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/anatomy/index.html</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -16922,17 +16922,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuration</t>
+          <t xml:space="preserve">Casebook</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/configuration/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/casebook/index.html</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -16952,7 +16952,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -16987,22 +16987,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pricing</t>
+          <t xml:space="preserve">Configuration</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/configuration/index.html</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -17012,12 +17012,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -17052,22 +17052,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operations</t>
+          <t xml:space="preserve">Pricing</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/operations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/index.html</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -17077,12 +17077,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -17117,17 +17117,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenarios</t>
+          <t xml:space="preserve">Operations</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/scenarios/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/operations/index.html</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -17177,27 +17177,27 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Procurement / MM</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procurement</t>
+          <t xml:space="preserve">Scenarios</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/scenarios/index.html</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
+          <t xml:space="preserve">Procurement</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/index.html</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -17267,12 +17267,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">logistics-p2p</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -17312,17 +17312,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -17360,7 +17360,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -17377,17 +17377,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -17425,7 +17425,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -17442,17 +17442,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -17507,17 +17507,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -17567,22 +17567,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Production / PP</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production</t>
+          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -17592,12 +17592,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J211" t="n">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -17632,22 +17632,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Quality Management</t>
+          <t xml:space="preserve">SAP Production / PP</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality Management</t>
+          <t xml:space="preserve">Production</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -17697,27 +17697,27 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Quality Management</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Quality Management</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J213" t="n">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -17762,27 +17762,27 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -17792,17 +17792,17 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-diagnostics</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J214" t="n">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -17827,22 +17827,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Diagnostics</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -17897,22 +17897,22 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Sales Diagnostics</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -17962,17 +17962,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -18010,7 +18010,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -18027,17 +18027,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -18092,17 +18092,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -18122,12 +18122,12 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J219" t="n">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -18157,22 +18157,22 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Processes</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -18182,12 +18182,12 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -18205,7 +18205,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -18217,27 +18217,27 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Sales Processes</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -18247,12 +18247,12 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -18282,27 +18282,27 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -18312,12 +18312,12 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -18347,27 +18347,27 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -18377,7 +18377,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J223" t="n">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -18417,17 +18417,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -18477,27 +18477,27 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Shipping</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -18507,7 +18507,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -18517,7 +18517,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J225" t="n">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -18542,27 +18542,27 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP Shipping</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Shipping</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-shipping</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J226" t="n">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -18607,37 +18607,37 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J227" t="n">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -18672,37 +18672,37 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J228" t="n">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -18742,22 +18742,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Management</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -18767,7 +18767,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -18802,27 +18802,27 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Transportation Management</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -18832,17 +18832,17 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J230" t="n">
@@ -18855,7 +18855,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -18867,22 +18867,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -18902,12 +18902,12 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J231" t="n">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -18932,27 +18932,27 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erp Diagnostic Practice</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -18962,17 +18962,17 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J232" t="n">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -19002,17 +19002,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
+          <t xml:space="preserve">Erp Diagnostic Practice</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
+          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -19062,42 +19062,42 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -19115,7 +19115,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -19127,42 +19127,42 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/index.md</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -19180,7 +19180,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -19197,17 +19197,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -19222,7 +19222,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -19245,7 +19245,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -19262,17 +19262,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -19310,7 +19310,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -19327,17 +19327,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -19375,7 +19375,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -19392,17 +19392,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19417,7 +19417,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19452,22 +19452,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19517,42 +19517,42 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -19570,7 +19570,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -19587,37 +19587,37 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19652,17 +19652,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19700,7 +19700,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19717,37 +19717,37 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19782,17 +19782,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -19812,7 +19812,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -19830,7 +19830,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19847,17 +19847,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19912,17 +19912,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19977,17 +19977,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20042,37 +20042,37 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -20090,7 +20090,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20102,37 +20102,37 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -20142,7 +20142,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J250" t="n">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -20167,27 +20167,27 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -20197,7 +20197,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -20207,7 +20207,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J251" t="n">
@@ -20220,7 +20220,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -20232,37 +20232,37 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/templates/</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/templates/index.md</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -20285,7 +20285,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -20297,70 +20297,135 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>1</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C254" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E254" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
+      <c r="F254" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
+      <c r="G254" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J253" t="n">
-        <v>1</v>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L253" t="inlineStr">
+      <c r="I254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>1</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M253" t="inlineStr">
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M253"/>
+  <autoFilter ref="A1:M254"/>
 </worksheet>
 </file>
 
@@ -20706,7 +20771,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9">
@@ -177,7 +177,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">38.7%</t>
+          <t xml:space="preserve">36.0%</t>
         </is>
       </c>
     </row>
@@ -13997,22 +13997,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Batch Master</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/batch-master/</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/batch-master/index.html</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -14022,17 +14022,17 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/batch-master/</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14062,22 +14062,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material Behavior</t>
+          <t xml:space="preserve">Bp Addresses</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/material-behavior/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/bp-addresses/</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/material-behavior/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/bp-addresses/index.html</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -14087,17 +14087,17 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/material-behavior/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/bp-addresses/</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -14122,22 +14122,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
+          <t xml:space="preserve">Business Partner</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/business-partner/</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/architecture/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/business-partner/index.html</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/business-partner/</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -14187,47 +14187,47 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Credit Management</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lead Assessment Drills — Enterprise Context Lab</t>
+          <t xml:space="preserve">Credit Master Data</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/assessment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/credit-master-data/</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/assessment/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/credit-master-data/index.html</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, lead-decision, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/assessment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/credit-master-data/</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -14252,22 +14252,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">Cross Selling</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/cross-selling/</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/build-runtime/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/cross-selling/index.html</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/cross-selling/</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -14317,47 +14317,47 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Consolidation &amp; Golden Record — Enterprise Context Lab</t>
+          <t xml:space="preserve">Customer Hierarchy</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/customer-hierarchy/</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/customer-hierarchy/index.html</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/customer-hierarchy/</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -14382,47 +14382,47 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Matching &amp; Survivorship — Enterprise Context Lab</t>
+          <t xml:space="preserve">Customer Material</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/survivorship/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/customer-material/</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/survivorship/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/customer-material/index.html</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/survivorship/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/customer-material/</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -14447,22 +14447,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">Free Goods</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/free-goods/</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/engineering/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/free-goods/index.html</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/free-goods/</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -14512,27 +14512,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/index.html</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -14542,12 +14542,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -14577,22 +14577,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
+          <t xml:space="preserve">Item Proposal</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/item-proposal/</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/deployments/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/item-proposal/index.html</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14612,12 +14612,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/item-proposal/</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -14642,22 +14642,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">Listing Exclusion</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/listing-exclusion/</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/entity-map/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/listing-exclusion/index.html</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, integration-observability, integration-recovery</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/listing-exclusion/</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -14707,47 +14707,47 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner, Customer &amp; Supplier — Enterprise Context Lab</t>
+          <t xml:space="preserve">Master Texts</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/master-texts/</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/master-texts/index.html</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/master-texts/</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -14772,47 +14772,47 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Domain Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">Material Determination</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/material-determination/</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/material-determination/index.html</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/material-determination/</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -14837,22 +14837,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">Partner Functions</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/partner-functions/</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/entity-map/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/partner-functions/index.html</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14872,12 +14872,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/partner-functions/</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -14902,47 +14902,47 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Domain — Enterprise Context Lab</t>
+          <t xml:space="preserve">Pricing Condition Record</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/pricing-condition-record/</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/pricing-condition-record/index.html</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/pricing-condition-record/</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -14967,22 +14967,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">Product</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/product/</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/extensions/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/product/index.html</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15002,12 +15002,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/product/</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -15032,22 +15032,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
+          <t xml:space="preserve">Product Hierarchy</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/product-hierarchy/</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/brfplus-rules/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/product-hierarchy/index.html</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15067,12 +15067,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/product-hierarchy/</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -15097,47 +15097,47 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Change Request Type Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">Sales Bom</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/sales-bom/</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/change-request-matrix/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/sales-bom/index.html</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-decision, logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/sales-bom/</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -15162,47 +15162,47 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Engine — Enterprise Context Lab</t>
+          <t xml:space="preserve">Units Of Measure</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/units-of-measure/</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/units-of-measure/index.html</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-decision, logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/units-of-measure/</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -15227,22 +15227,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
+          <t xml:space="preserve">Variant Configuration</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/variant-configuration/</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/impact/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/variant-configuration/index.html</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -15262,12 +15262,12 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/variant-configuration/</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15292,27 +15292,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
+          <t xml:space="preserve">Material Behavior</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/material-behavior/</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/implementation/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/material-behavior/index.html</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -15322,17 +15322,17 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J176" t="n">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/material-behavior/</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15357,27 +15357,27 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Governance</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data Governance — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/architecture/index.md</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -15387,17 +15387,17 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -15427,37 +15427,37 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Lead Assessment Drills — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/assessment/</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/interfaces/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/assessment/index.md</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, lead-decision, logistics-mdg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/assessment/</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -15492,17 +15492,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/lineage/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/build-runtime/index.md</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
+          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -15552,42 +15552,42 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Consolidation &amp; Golden Record — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/cases/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/index.md</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -15617,42 +15617,42 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Matching &amp; Survivorship — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/survivorship/</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/survivorship/index.md</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/survivorship/</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -15687,17 +15687,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/migration/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/engineering/index.md</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -15752,17 +15752,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/ownership/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/index.md</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-master-data</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -15817,17 +15817,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/processes/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/deployments/index.md</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -15847,12 +15847,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
+          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -15865,7 +15865,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -15877,22 +15877,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/reasoning/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/entity-map/index.md</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
+          <t xml:space="preserve">sales-o2c, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -15942,22 +15942,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Replication &amp; Distribution — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Business Partner, Customer &amp; Supplier — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/replication/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/index.md</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg, sales-o2c</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -16012,17 +16012,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG DRF Operations &amp; Replay — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Domain Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/replication/operations/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/index.md</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -16077,17 +16077,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/scenario/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/entity-map/index.md</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -16107,12 +16107,12 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
+          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -16137,22 +16137,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA API-Led Migration — Design, Restart and Cutover</t>
+          <t xml:space="preserve">SAP MDG Material Domain — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/api-led-migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/api-led-migration.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/index.md</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-patterns, integration-recovery</t>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/api-led-migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -16202,42 +16202,42 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Cutover — Rehearsal, Delta and Reconciliation</t>
+          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/cutover/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/cutover.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/extensions/index.md</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-recovery, logistics-inventory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/cutover/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -16267,42 +16267,42 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Design Register — Object Control</t>
+          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/design-register/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/design-register.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/brfplus-rules/index.md</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/design-register/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -16332,22 +16332,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Domain Playbooks — SD, MM, PP, EWM, FI and CO</t>
+          <t xml:space="preserve">SAP MDG Change Request Type Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/domain-playbooks/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/domain-playbooks.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/change-request-matrix/index.md</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, logistics-production-quality, sales-o2c</t>
+          <t xml:space="preserve">lead-decision, logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/domain-playbooks/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -16397,22 +16397,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Greenfield Migration — Architecture and Data Load</t>
+          <t xml:space="preserve">SAP MDG Governance Engine — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/index.md</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, logistics-master-data</t>
+          <t xml:space="preserve">lead-decision, logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -16462,42 +16462,42 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Lead Assessment — Architecture Drills</t>
+          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/lead-assessment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/lead-assessment.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/impact/index.md</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -16515,7 +16515,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/lead-assessment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -16527,47 +16527,47 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Factory — Governance, Mock Cycles and Ownership</t>
+          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/migration-factory/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/migration-factory.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/implementation/index.md</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-recovery, lead-decision</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J195" t="n">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/migration-factory/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -16592,22 +16592,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">Data Governance</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Object Catalog — Greenfield Load Scope</t>
+          <t xml:space="preserve">SAP Master Data Governance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/object-catalog/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/object-catalog.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/index.md</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J196" t="n">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/object-catalog/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -16657,42 +16657,42 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Tools — Cockpit, APIs and Integration</t>
+          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/tooling/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/tooling.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/interfaces/index.md</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, integration-deployment, integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/tooling/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -16722,22 +16722,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
+          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/model/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/lineage/index.md</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -16757,12 +16757,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
+          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J198" t="n">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -16787,42 +16787,42 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Performance</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Performance and Technical Operations — Practical S/4HANA Troubleshooting</t>
+          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/performance/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/performance/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/cases/index.md</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-observability, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/performance/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -16852,22 +16852,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anatomy</t>
+          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/anatomy/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/index.md</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -16917,22 +16917,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casebook</t>
+          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/casebook/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/migration/index.md</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -16952,7 +16952,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -16982,22 +16982,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuration</t>
+          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/configuration/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/ownership/index.md</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
+          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-master-data</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -17047,27 +17047,27 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pricing</t>
+          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/processes/index.md</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -17077,17 +17077,17 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J203" t="n">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -17112,22 +17112,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operations</t>
+          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/operations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/reasoning/index.md</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -17177,42 +17177,42 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenarios</t>
+          <t xml:space="preserve">SAP MDG Replication &amp; Distribution — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/scenarios/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/replication/index.md</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Procurement / MM</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procurement</t>
+          <t xml:space="preserve">SAP MDG DRF Operations &amp; Replay — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/operations/</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/replication/operations/index.md</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -17267,12 +17267,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p</t>
+          <t xml:space="preserve">integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/operations/</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -17307,42 +17307,42 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Procurement / MM</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
+          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/scenario/index.md</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -17360,7 +17360,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -17372,22 +17372,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Procurement / MM</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">SAP S/4HANA API-Led Migration — Design, Restart and Cutover</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/api-led-migration/</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/api-led-migration.md</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
+          <t xml:space="preserve">delivery-release, integration-patterns, integration-recovery</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -17425,7 +17425,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/api-led-migration/</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -17437,22 +17437,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Procurement / MM</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Cutover — Rehearsal, Delta and Reconciliation</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/cutover/</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/cutover.md</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">delivery-release, integration-recovery, logistics-inventory</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/cutover/</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -17502,22 +17502,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Procurement / MM</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Design Register — Object Control</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/design-register/</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/design-register.md</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/design-register/</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -17567,22 +17567,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Procurement / MM</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Domain Playbooks — SD, MM, PP, EWM, FI and CO</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/domain-playbooks/</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/domain-playbooks.md</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">logistics-p2p, logistics-production-quality, sales-o2c</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/domain-playbooks/</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -17632,22 +17632,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Production / PP</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production</t>
+          <t xml:space="preserve">SAP S/4HANA Greenfield Migration — Architecture and Data Load</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/index.md</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, logistics-master-data</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -17697,22 +17697,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Quality Management</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality Management</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Lead Assessment — Architecture Drills</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/lead-assessment/</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/lead-assessment.md</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -17722,12 +17722,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -17737,7 +17737,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J213" t="n">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/lead-assessment/</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -17762,42 +17762,42 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Factory — Governance, Mock Cycles and Ownership</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/migration-factory/</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/migration-factory.md</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-release, integration-recovery, lead-decision</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/migration-factory/</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -17827,22 +17827,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Object Catalog — Greenfield Load Scope</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/object-catalog/</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/object-catalog.md</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -17852,12 +17852,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-diagnostics</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J215" t="n">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/object-catalog/</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -17892,22 +17892,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Diagnostics</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Tools — Cockpit, APIs and Integration</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/tooling/</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/tooling.md</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -17917,12 +17917,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-diagnostics</t>
+          <t xml:space="preserve">delivery-cicd, integration-deployment, integration-patterns</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/tooling/</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -17957,22 +17957,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/model/index.md</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -18010,7 +18010,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -18022,37 +18022,37 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Performance</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">SAP Performance and Technical Operations — Practical S/4HANA Troubleshooting</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/performance/</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/performance/index.md</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-observability, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J218" t="n">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/performance/</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -18087,22 +18087,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Anatomy</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/anatomy/index.html</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -18122,12 +18122,12 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J219" t="n">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -18152,22 +18152,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Casebook</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/casebook/index.html</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -18205,7 +18205,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -18217,27 +18217,27 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Processes</t>
+          <t xml:space="preserve">Configuration</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/configuration/index.html</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -18247,12 +18247,12 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -18282,27 +18282,27 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Pricing</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/index.html</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -18312,12 +18312,12 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -18347,27 +18347,27 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Operations</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/operations/index.html</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -18377,12 +18377,12 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -18412,22 +18412,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Scenarios</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/scenarios/index.html</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -18447,12 +18447,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J224" t="n">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -18477,27 +18477,27 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Procurement</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/index.html</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -18507,7 +18507,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-p2p</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -18517,7 +18517,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J225" t="n">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -18542,22 +18542,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Shipping</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping</t>
+          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -18567,12 +18567,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-shipping</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -18607,37 +18607,37 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J227" t="n">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -18672,22 +18672,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
+          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -18702,7 +18702,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -18737,37 +18737,37 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J229" t="n">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -18802,22 +18802,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Management</t>
+          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -18827,12 +18827,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J230" t="n">
@@ -18855,7 +18855,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -18867,27 +18867,27 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Production / PP</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Production</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -18897,17 +18897,17 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J231" t="n">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -18932,27 +18932,27 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">SAP Quality Management</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Quality Management</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -18962,12 +18962,12 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -19002,22 +19002,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erp Diagnostic Practice</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -19027,12 +19027,12 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -19062,22 +19062,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -19087,12 +19087,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J234" t="n">
@@ -19115,7 +19115,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -19127,27 +19127,27 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">Sales Diagnostics</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -19157,17 +19157,17 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J235" t="n">
@@ -19180,7 +19180,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -19192,37 +19192,37 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -19232,7 +19232,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J236" t="n">
@@ -19245,7 +19245,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -19257,37 +19257,37 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J237" t="n">
@@ -19310,7 +19310,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -19322,37 +19322,37 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -19362,7 +19362,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J238" t="n">
@@ -19375,7 +19375,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -19387,42 +19387,42 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19452,22 +19452,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">Sales Processes</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19517,42 +19517,42 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -19570,7 +19570,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -19582,27 +19582,27 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -19612,12 +19612,12 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19647,37 +19647,37 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J243" t="n">
@@ -19700,7 +19700,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19712,37 +19712,37 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J244" t="n">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19777,27 +19777,27 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Shipping</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">Shipping</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -19807,12 +19807,12 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-shipping</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -19830,7 +19830,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19842,22 +19842,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -19877,12 +19877,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J246" t="n">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19907,42 +19907,42 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19972,22 +19972,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20007,12 +20007,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J248" t="n">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20037,27 +20037,27 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">Transportation Management</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -20067,17 +20067,17 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J249" t="n">
@@ -20090,7 +20090,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20102,42 +20102,42 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -20167,22 +20167,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -20220,7 +20220,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -20232,22 +20232,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">Erp Diagnostic Practice</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -20272,7 +20272,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J252" t="n">
@@ -20285,7 +20285,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -20297,37 +20297,37 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -20337,7 +20337,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J253" t="n">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -20362,70 +20362,1305 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/index.md</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_decision</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>1</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J255" t="n">
+        <v>1</v>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>1</v>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>1</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>1</v>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J259" t="n">
+        <v>1</v>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI / RAG / Agents</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J260" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_decision</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J261" t="n">
+        <v>1</v>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>1</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_decision</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>1</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_decision</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>1</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_decision</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>1</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_decision</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J267" t="n">
+        <v>1</v>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_decision</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>1</v>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reusable Data Procedures</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reusable Data Procedures</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_decision</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>1</v>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/index.md</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-memory</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>1</v>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J272" t="n">
+        <v>1</v>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C273" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D273" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E273" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
+      <c r="F273" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
+      <c r="G273" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J254" t="n">
-        <v>1</v>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L254" t="inlineStr">
+      <c r="I273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J273" t="n">
+        <v>1</v>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr">
+      <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M254"/>
+  <autoFilter ref="A1:M273"/>
 </worksheet>
 </file>
 
@@ -20837,13 +22072,13 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -21585,13 +22820,13 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -21893,13 +23128,13 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E66" t="n">
         <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -26571,32 +27806,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
+          <t xml:space="preserve">Batch Master</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/batch-master/</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/batch-master/</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -26608,32 +27843,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">Bp Addresses</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/bp-addresses/</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/bp-addresses/</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -26645,32 +27880,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">Business Partner</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/business-partner/</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/business-partner/</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -26682,32 +27917,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Credit Management</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">Credit Master Data</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/credit-master-data/</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/credit-master-data/</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -26719,32 +27954,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
+          <t xml:space="preserve">Cross Selling</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/cross-selling/</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/cross-selling/</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -26756,32 +27991,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">Customer Hierarchy</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/customer-hierarchy/</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, integration-observability, integration-recovery</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/customer-hierarchy/</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -26793,32 +28028,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">Customer Material</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/customer-material/</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/customer-material/</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -26830,32 +28065,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">Free Goods</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/free-goods/</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/free-goods/</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -26867,32 +28102,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
+          <t xml:space="preserve">Item Proposal</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/item-proposal/</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/item-proposal/</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -26904,32 +28139,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
+          <t xml:space="preserve">Listing Exclusion</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/listing-exclusion/</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/listing-exclusion/</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -26941,32 +28176,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
+          <t xml:space="preserve">Master Texts</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/master-texts/</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/master-texts/</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -26978,32 +28213,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
+          <t xml:space="preserve">Material Determination</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/material-determination/</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/material-determination/</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -27015,32 +28250,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
+          <t xml:space="preserve">Partner Functions</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/partner-functions/</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/partner-functions/</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -27052,32 +28287,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
+          <t xml:space="preserve">Pricing Condition Record</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/pricing-condition-record/</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/pricing-condition-record/</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -27089,32 +28324,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
+          <t xml:space="preserve">Product</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/product/</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/product/</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -27126,32 +28361,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
+          <t xml:space="preserve">Product Hierarchy</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/product-hierarchy/</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/product-hierarchy/</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -27163,32 +28398,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
+          <t xml:space="preserve">Sales Bom</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/sales-bom/</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-master-data</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/sales-bom/</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -27200,22 +28435,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
+          <t xml:space="preserve">Units Of Measure</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/units-of-measure/</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -27225,7 +28460,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/units-of-measure/</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -27237,32 +28472,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
+          <t xml:space="preserve">Variant Configuration</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/variant-configuration/</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/variant-configuration/</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -27279,17 +28514,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
+          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -27299,7 +28534,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -27311,32 +28546,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
+          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
+          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -27348,22 +28583,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anatomy</t>
+          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -27373,7 +28608,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -27385,22 +28620,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casebook</t>
+          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -27410,7 +28645,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -27422,32 +28657,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuration</t>
+          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
+          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -27459,22 +28694,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operations</t>
+          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">sales-o2c, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -27484,7 +28719,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -27496,32 +28731,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenarios</t>
+          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -27533,22 +28768,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
+          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -27558,7 +28793,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -27570,32 +28805,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -27607,32 +28842,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -27644,22 +28879,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -27669,7 +28904,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -27681,22 +28916,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -27706,7 +28941,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -27718,22 +28953,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27743,7 +28978,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -27755,32 +28990,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -27792,32 +29027,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -27829,32 +29064,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -27866,32 +29101,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-master-data</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -27903,32 +29138,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -27940,32 +29175,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve">delivery-testing, delivery-lifecycle, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -27977,22 +29212,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
+          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -28002,7 +29237,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -28014,32 +29249,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -28051,22 +29286,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">Anatomy</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -28076,7 +29311,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -28088,22 +29323,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">Casebook</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -28113,7 +29348,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -28125,22 +29360,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">Configuration</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -28150,7 +29385,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -28162,22 +29397,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">Operations</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -28187,7 +29422,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -28199,22 +29434,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">Scenarios</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -28224,7 +29459,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -28236,32 +29471,32 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -28273,42 +29508,745 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t xml:space="preserve">SAP Sales / SD</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales Order</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Sales / SD</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control Plane</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Sales / SD</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Returns Claims</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Sales / SD</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coverage</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integration Architecture</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrations</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integration-patterns</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Sales / SD</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Derivation</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Sales / SD</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanisms</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Tax</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tax</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP TM</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charges</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integration Architecture</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integrations</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integration-patterns</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP TM</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planning</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logistics-tm</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-ams, delivery-memory, delivery-testing</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reusable Data Procedures</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reusable Data Procedures</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G156"/>
+  <autoFilter ref="A1:G175"/>
 </worksheet>
 </file>
 

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.2%</t>
+          <t xml:space="preserve">37.4%</t>
         </is>
       </c>
     </row>
@@ -1639,6 +1639,7 @@
       <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">Procurement — https://dkharlanau.github.io/labs/enterprise-context/procurement/
+Material Valuation — https://dkharlanau.github.io/labs/enterprise-context/procurement/material-valuation/
 Condition Contract Management — https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/
 Kanban Replenishment Strategies — https://dkharlanau.github.io/labs/enterprise-context/kanban/replenishment-strategies/
 Kanban Runtime Flows — https://dkharlanau.github.io/labs/enterprise-context/kanban/runtime-flows/
@@ -1711,6 +1712,7 @@
       <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">Inventory Management — https://dkharlanau.github.io/labs/enterprise-context/inventory-management/
+Material Valuation — https://dkharlanau.github.io/labs/enterprise-context/procurement/material-valuation/
 Kanban Statuses and Signals — https://dkharlanau.github.io/labs/enterprise-context/kanban/statuses-signals/
 Kanban Operations and Diagnostics — https://dkharlanau.github.io/labs/enterprise-context/kanban/operations-diagnostics/</t>
         </is>
@@ -15080,7 +15082,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg, sales-o2c</t>
+          <t xml:space="preserve">logistics-inventory, logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -17225,7 +17227,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
+          <t xml:space="preserve">sales-o2c, logistics-inventory, delivery-testing</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -17615,7 +17617,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
+          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-p2p</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -19340,17 +19342,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
+          <t xml:space="preserve">Material Valuation in Procurement — Standard Price, Moving Average Price and FI Postings</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/material-valuation/</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/material-valuation/index.md</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -19365,7 +19367,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">logistics-inventory, logistics-p2p</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -19388,7 +19390,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/material-valuation/</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -19405,17 +19407,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19430,7 +19432,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -19453,7 +19455,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19470,17 +19472,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -19495,7 +19497,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -19518,7 +19520,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19535,17 +19537,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -19560,7 +19562,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -19583,7 +19585,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -19600,17 +19602,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -19625,7 +19627,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -19648,7 +19650,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19665,37 +19667,37 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax Code Determination in Purchasing &amp; Invoice Receipt — SAP S/4HANA MM</t>
+          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/tax-code-determination/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/tax-code-determination/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, delivery-testing, integration-development</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -19713,7 +19715,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/tax-code-determination/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19725,27 +19727,27 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Production / PP</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production</t>
+          <t xml:space="preserve">Tax Code Determination in Purchasing &amp; Invoice Receipt — SAP S/4HANA MM</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/tax-code-determination/</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/tax-code-determination/index.md</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -19755,17 +19757,17 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-p2p, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J244" t="n">
@@ -19778,7 +19780,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/tax-code-determination/</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19790,22 +19792,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Quality Management</t>
+          <t xml:space="preserve">SAP Production / PP</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality Management</t>
+          <t xml:space="preserve">Production</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -19843,7 +19845,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19855,27 +19857,27 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Quality Management</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Quality Management</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -19885,17 +19887,17 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, ai-evaluation, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J246" t="n">
@@ -19908,7 +19910,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19920,27 +19922,27 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -19950,17 +19952,17 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-diagnostics</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, ai-evaluation, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J247" t="n">
@@ -19973,7 +19975,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19985,22 +19987,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Diagnostics</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20038,7 +20040,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20050,22 +20052,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Fiori Apps</t>
+          <t xml:space="preserve">Sales Diagnostics</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-fiori-apps/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-fiori-apps/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -20080,7 +20082,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -20090,7 +20092,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J249" t="n">
@@ -20103,7 +20105,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-fiori-apps/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20115,27 +20117,27 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Sales Fiori Apps</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-fiori-apps/</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-fiori-apps/index.html</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -20145,12 +20147,12 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -20168,7 +20170,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-fiori-apps/</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -20185,17 +20187,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -20233,7 +20235,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -20250,17 +20252,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -20298,7 +20300,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -20315,17 +20317,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20345,7 +20347,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -20363,7 +20365,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -20380,17 +20382,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer Consignment</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/customer-consignment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/customer-consignment/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -20410,7 +20412,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -20428,7 +20430,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/customer-consignment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -20445,17 +20447,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t xml:space="preserve">External Procurement</t>
+          <t xml:space="preserve">Customer Consignment</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/external-procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/customer-consignment/</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/external-procurement/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/customer-consignment/index.html</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -20493,7 +20495,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/external-procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/customer-consignment/</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -20510,17 +20512,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immediate Sales</t>
+          <t xml:space="preserve">External Procurement</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/immediate-sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/external-procurement/</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/immediate-sales/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/external-procurement/index.html</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -20558,7 +20560,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/immediate-sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/external-procurement/</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -20575,22 +20577,22 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Processes</t>
+          <t xml:space="preserve">Immediate Sales</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/immediate-sales/</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/immediate-sales/index.html</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -20600,14 +20602,14 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
           <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I257" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
@@ -20623,7 +20625,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/immediate-sales/</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -20635,27 +20637,27 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Sales Processes</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -20665,12 +20667,12 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -20688,7 +20690,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -20700,22 +20702,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intercompany Sales</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/intercompany-sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/intercompany-sales/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -20735,7 +20737,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">integration-patterns, sales-o2c</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -20753,7 +20755,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/intercompany-sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -20770,17 +20772,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make To Order</t>
+          <t xml:space="preserve">Intercompany Sales</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/make-to-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/intercompany-sales/</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/make-to-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/intercompany-sales/index.html</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -20818,7 +20820,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/make-to-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/intercompany-sales/</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -20830,27 +20832,27 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Make To Order</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/make-to-order/</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/make-to-order/index.html</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -20860,14 +20862,14 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
           <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I261" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
@@ -20883,7 +20885,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/make-to-order/</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -20895,27 +20897,27 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -20925,12 +20927,12 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -20948,7 +20950,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -20965,17 +20967,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -21013,7 +21015,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -21030,17 +21032,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Free Of Charge</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/returns-free-of-charge/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -21078,7 +21080,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -21095,17 +21097,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stock Transfer Orders</t>
+          <t xml:space="preserve">Returns Free Of Charge</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/stock-transfer-orders/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/returns-free-of-charge/index.html</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -21143,7 +21145,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -21155,27 +21157,27 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Shipping</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping</t>
+          <t xml:space="preserve">Stock Transfer Orders</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/stock-transfer-orders/index.html</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -21185,12 +21187,12 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -21208,7 +21210,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -21220,27 +21222,27 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP Shipping</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Shipping</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -21250,12 +21252,12 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-shipping</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -21273,7 +21275,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -21285,42 +21287,42 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -21338,7 +21340,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -21350,42 +21352,42 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -21403,7 +21405,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -21420,22 +21422,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Management</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -21445,17 +21447,17 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J270" t="n">
@@ -21468,7 +21470,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -21480,27 +21482,27 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Transportation Management</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -21510,17 +21512,17 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J271" t="n">
@@ -21533,7 +21535,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -21545,22 +21547,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -21580,7 +21582,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">integration-patterns, sales-o2c</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -21598,7 +21600,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -21610,27 +21612,27 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erp Diagnostic Practice</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -21640,12 +21642,12 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -21663,7 +21665,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -21680,17 +21682,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
+          <t xml:space="preserve">Erp Diagnostic Practice</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
+          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -21700,12 +21702,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -21728,7 +21730,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -21740,42 +21742,42 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-ams, delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -21793,7 +21795,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -21805,42 +21807,42 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/index.md</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, delivery-ams, delivery-memory</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -21858,7 +21860,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -21875,17 +21877,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -21900,7 +21902,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -21923,7 +21925,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -21940,17 +21942,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -21965,7 +21967,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -21988,7 +21990,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -22005,17 +22007,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -22030,7 +22032,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -22053,7 +22055,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -22070,17 +22072,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -22095,7 +22097,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -22118,7 +22120,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -22130,22 +22132,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -22160,7 +22162,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -22183,7 +22185,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -22195,42 +22197,42 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -22248,7 +22250,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -22265,37 +22267,37 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -22313,7 +22315,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -22330,17 +22332,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -22355,7 +22357,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22378,7 +22380,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -22395,37 +22397,37 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-ams, logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -22443,7 +22445,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -22460,17 +22462,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -22490,7 +22492,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">sales-o2c, delivery-ams, logistics-tm</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -22508,7 +22510,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -22525,17 +22527,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -22555,7 +22557,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-ams</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -22573,7 +22575,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -22590,17 +22592,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -22620,7 +22622,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-ams</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -22638,7 +22640,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -22655,17 +22657,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -22685,7 +22687,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -22703,7 +22705,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -22720,37 +22722,37 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -22768,7 +22770,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -22780,42 +22782,42 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -22833,7 +22835,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -22845,27 +22847,27 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -22875,17 +22877,17 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J292" t="n">
@@ -22898,7 +22900,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -22910,37 +22912,37 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/templates/</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/templates/index.md</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -22963,7 +22965,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -22975,70 +22977,135 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J294" t="n">
+        <v>1</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
+      <c r="C295" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr">
+      <c r="D295" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
+      <c r="E295" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
+      <c r="F295" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
+      <c r="G295" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, sales-o2c, ai-agents-mcp</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J294" t="n">
-        <v>1</v>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L294" t="inlineStr">
+      <c r="I295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J295" t="n">
+        <v>1</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M294" t="inlineStr">
+      <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M294"/>
+  <autoFilter ref="A1:M295"/>
 </worksheet>
 </file>
 
@@ -24660,10 +24727,10 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
+        <v>8</v>
+      </c>
+      <c r="E73" t="n">
         <v>7</v>
-      </c>
-      <c r="E73" t="n">
-        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
@@ -29680,7 +29747,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg, sales-o2c</t>
+          <t xml:space="preserve">logistics-inventory, logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -30309,7 +30376,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
+          <t xml:space="preserve">sales-o2c, logistics-inventory, delivery-testing</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -30494,7 +30561,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
+          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-p2p</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -177,7 +177,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.4%</t>
+          <t xml:space="preserve">37.3%</t>
         </is>
       </c>
     </row>
@@ -19407,37 +19407,37 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
+          <t xml:space="preserve">Purchasing Customizing</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/purchasing-customizing/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/purchasing-customizing/index.html</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/purchasing-customizing/</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19472,17 +19472,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19537,17 +19537,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -19602,17 +19602,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19667,17 +19667,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19732,37 +19732,37 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax Code Determination in Purchasing &amp; Invoice Receipt — SAP S/4HANA MM</t>
+          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/tax-code-determination/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/tax-code-determination/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, delivery-testing, integration-development</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -19780,7 +19780,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/tax-code-determination/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19792,27 +19792,27 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Production / PP</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production</t>
+          <t xml:space="preserve">Tax Code Determination in Purchasing &amp; Invoice Receipt — SAP S/4HANA MM</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/tax-code-determination/</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/tax-code-determination/index.md</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -19822,17 +19822,17 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-p2p, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J245" t="n">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/tax-code-determination/</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19857,22 +19857,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Quality Management</t>
+          <t xml:space="preserve">SAP Production / PP</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality Management</t>
+          <t xml:space="preserve">Production</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19922,27 +19922,27 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Quality Management</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Quality Management</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -19952,17 +19952,17 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, ai-evaluation, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J247" t="n">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19987,27 +19987,27 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -20017,17 +20017,17 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-diagnostics</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, ai-evaluation, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J248" t="n">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20052,22 +20052,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Diagnostics</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20117,22 +20117,22 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Fiori Apps</t>
+          <t xml:space="preserve">Sales Diagnostics</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-fiori-apps/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-fiori-apps/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -20147,7 +20147,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -20157,7 +20157,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J250" t="n">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-fiori-apps/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -20182,27 +20182,27 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Sales Fiori Apps</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-fiori-apps/</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-fiori-apps/index.html</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -20212,12 +20212,12 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-fiori-apps/</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -20252,17 +20252,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -20317,17 +20317,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20365,7 +20365,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -20382,17 +20382,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -20447,17 +20447,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer Consignment</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/customer-consignment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/customer-consignment/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/customer-consignment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -20512,17 +20512,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t xml:space="preserve">External Procurement</t>
+          <t xml:space="preserve">Customer Consignment</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/external-procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/customer-consignment/</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/external-procurement/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/customer-consignment/index.html</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -20560,7 +20560,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/external-procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/customer-consignment/</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -20577,17 +20577,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immediate Sales</t>
+          <t xml:space="preserve">External Procurement</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/immediate-sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/external-procurement/</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/immediate-sales/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/external-procurement/index.html</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/immediate-sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/external-procurement/</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Processes</t>
+          <t xml:space="preserve">Immediate Sales</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/immediate-sales/</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/immediate-sales/index.html</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -20667,14 +20667,14 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
           <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I258" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
@@ -20690,7 +20690,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/immediate-sales/</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -20702,27 +20702,27 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Sales Processes</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -20732,12 +20732,12 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -20755,7 +20755,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -20767,22 +20767,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intercompany Sales</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/intercompany-sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/intercompany-sales/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">integration-patterns, sales-o2c</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/intercompany-sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -20837,17 +20837,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make To Order</t>
+          <t xml:space="preserve">Intercompany Sales</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/make-to-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/intercompany-sales/</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/make-to-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/intercompany-sales/index.html</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -20885,7 +20885,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/make-to-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/intercompany-sales/</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -20897,27 +20897,27 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Make To Order</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/make-to-order/</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/make-to-order/index.html</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -20927,14 +20927,14 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
           <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I262" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
@@ -20950,7 +20950,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/make-to-order/</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -20962,27 +20962,27 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -20992,12 +20992,12 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -21032,17 +21032,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -21097,17 +21097,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Free Of Charge</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/returns-free-of-charge/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -21145,7 +21145,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -21162,17 +21162,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stock Transfer Orders</t>
+          <t xml:space="preserve">Returns Free Of Charge</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/stock-transfer-orders/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/returns-free-of-charge/index.html</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -21222,27 +21222,27 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Shipping</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping</t>
+          <t xml:space="preserve">Stock Transfer Orders</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/stock-transfer-orders/index.html</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -21252,12 +21252,12 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -21275,7 +21275,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -21287,27 +21287,27 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP Shipping</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Shipping</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -21317,12 +21317,12 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-shipping</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -21352,42 +21352,42 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -21417,42 +21417,42 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -21487,22 +21487,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Management</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -21512,17 +21512,17 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J271" t="n">
@@ -21535,7 +21535,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -21547,27 +21547,27 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Transportation Management</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -21577,17 +21577,17 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J272" t="n">
@@ -21600,7 +21600,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -21612,22 +21612,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">integration-patterns, sales-o2c</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -21677,27 +21677,27 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erp Diagnostic Practice</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -21707,12 +21707,12 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -21747,17 +21747,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
+          <t xml:space="preserve">Erp Diagnostic Practice</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
+          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -21767,12 +21767,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -21807,42 +21807,42 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-ams, delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -21872,42 +21872,42 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/index.md</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, delivery-ams, delivery-memory</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -21925,7 +21925,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -21942,17 +21942,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -21967,7 +21967,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -21990,7 +21990,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -22007,17 +22007,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -22032,7 +22032,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -22055,7 +22055,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -22072,17 +22072,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -22137,17 +22137,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -22185,7 +22185,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -22197,22 +22197,22 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -22227,7 +22227,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -22250,7 +22250,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -22262,42 +22262,42 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -22315,7 +22315,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -22332,37 +22332,37 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -22397,17 +22397,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -22462,37 +22462,37 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-ams, logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -22510,7 +22510,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -22527,17 +22527,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">sales-o2c, delivery-ams, logistics-tm</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -22592,17 +22592,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-ams</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -22657,17 +22657,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-ams</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -22705,7 +22705,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -22722,17 +22722,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -22752,7 +22752,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -22787,37 +22787,37 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -22847,42 +22847,42 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -22912,27 +22912,27 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -22942,17 +22942,17 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J293" t="n">
@@ -22965,7 +22965,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -22977,37 +22977,37 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/templates/</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/templates/index.md</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -23042,70 +23042,135 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J295" t="n">
+        <v>1</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
+      <c r="B296" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr">
+      <c r="C296" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr">
+      <c r="D296" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr">
+      <c r="E296" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
+      <c r="F296" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
+      <c r="G296" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, sales-o2c, ai-agents-mcp</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J295" t="n">
-        <v>1</v>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L295" t="inlineStr">
+      <c r="I296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J296" t="n">
+        <v>1</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M295" t="inlineStr">
+      <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M295"/>
+  <autoFilter ref="A1:M296"/>
 </worksheet>
 </file>
 
@@ -24727,13 +24792,13 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E73" t="n">
         <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -30995,17 +31060,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax Code Determination in Purchasing &amp; Invoice Receipt — SAP S/4HANA MM</t>
+          <t xml:space="preserve">Purchasing Customizing</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/tax-code-determination/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/purchasing-customizing/</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, delivery-testing, integration-development</t>
+          <t xml:space="preserve">logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -31015,7 +31080,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/tax-code-determination/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/purchasing-customizing/</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -31027,22 +31092,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Tax Code Determination in Purchasing &amp; Invoice Receipt — SAP S/4HANA MM</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/tax-code-determination/</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, ai-evaluation, delivery-lifecycle</t>
+          <t xml:space="preserve">logistics-p2p, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -31052,7 +31117,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/tax-code-determination/</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -31064,22 +31129,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">sales-o2c, ai-evaluation, delivery-lifecycle</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -31089,7 +31154,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -31106,12 +31171,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31126,7 +31191,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -31143,12 +31208,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -31163,7 +31228,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -31180,17 +31245,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -31200,7 +31265,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -31217,17 +31282,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer Consignment</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/customer-consignment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -31237,7 +31302,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/customer-consignment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -31254,12 +31319,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">External Procurement</t>
+          <t xml:space="preserve">Customer Consignment</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/external-procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/customer-consignment/</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -31274,7 +31339,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/external-procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/customer-consignment/</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -31291,12 +31356,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immediate Sales</t>
+          <t xml:space="preserve">External Procurement</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/immediate-sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/external-procurement/</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -31311,7 +31376,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/immediate-sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/external-procurement/</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -31323,22 +31388,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Immediate Sales</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/immediate-sales/</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, sales-o2c</t>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -31348,7 +31413,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/immediate-sales/</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -31360,22 +31425,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intercompany Sales</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/intercompany-sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">integration-patterns, sales-o2c</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -31385,7 +31450,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/intercompany-sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -31402,12 +31467,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make To Order</t>
+          <t xml:space="preserve">Intercompany Sales</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/make-to-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/intercompany-sales/</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -31422,7 +31487,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/make-to-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/intercompany-sales/</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -31439,12 +31504,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Make To Order</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/make-to-order/</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -31459,7 +31524,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/make-to-order/</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -31476,12 +31541,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -31496,7 +31561,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -31513,12 +31578,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Free Of Charge</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -31533,7 +31598,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -31550,12 +31615,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stock Transfer Orders</t>
+          <t xml:space="preserve">Returns Free Of Charge</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -31570,7 +31635,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -31582,17 +31647,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Stock Transfer Orders</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -31607,7 +31672,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -31619,17 +31684,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -31644,7 +31709,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -31656,22 +31721,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, sales-o2c</t>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -31681,7 +31746,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -31693,22 +31758,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">integration-patterns, sales-o2c</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -31718,7 +31783,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -31730,22 +31795,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-ams, delivery-memory</t>
+          <t xml:space="preserve">logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -31755,7 +31820,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -31767,22 +31832,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">sales-o2c, delivery-ams, delivery-memory</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -31792,7 +31857,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -31809,17 +31874,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-ams, logistics-tm</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -31829,7 +31894,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -31846,17 +31911,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">sales-o2c, delivery-ams, logistics-tm</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -31866,7 +31931,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -31883,17 +31948,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-ams</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -31903,7 +31968,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -31920,17 +31985,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-ams</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -31940,7 +32005,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -31957,17 +32022,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -31977,7 +32042,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -31989,22 +32054,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -32014,7 +32079,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -32026,42 +32091,79 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Reusable Data Procedures</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reusable Data Procedures</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sales-o2c</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, sales-o2c, ai-agents-mcp</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G185"/>
+  <autoFilter ref="A1:G186"/>
 </worksheet>
 </file>
 

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9">
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.3%</t>
+          <t xml:space="preserve">37.5%</t>
         </is>
       </c>
     </row>
@@ -19862,17 +19862,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production</t>
+          <t xml:space="preserve">Consumption-Based Planning &amp; Forecasting — SAP S/4HANA MRP</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/consumption-based-planning/</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/consumption-based-planning.md</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -19882,12 +19882,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, logistics-production-quality</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J246" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/consumption-based-planning/</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19922,22 +19922,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Quality Management</t>
+          <t xml:space="preserve">SAP Production / PP</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality Management</t>
+          <t xml:space="preserve">Production</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19987,27 +19987,27 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Quality Management</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Quality Management</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -20017,17 +20017,17 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, ai-evaluation, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J248" t="n">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20052,27 +20052,27 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -20082,17 +20082,17 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-diagnostics</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, ai-evaluation, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J249" t="n">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20117,22 +20117,22 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Diagnostics</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -20182,22 +20182,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Fiori Apps</t>
+          <t xml:space="preserve">Sales Diagnostics</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-fiori-apps/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-fiori-apps/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -20212,7 +20212,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J251" t="n">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-fiori-apps/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -20247,27 +20247,27 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Sales Fiori Apps</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-fiori-apps/</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-fiori-apps/index.html</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -20277,12 +20277,12 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-fiori-apps/</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -20317,17 +20317,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20365,7 +20365,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -20382,17 +20382,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -20447,17 +20447,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -20512,17 +20512,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer Consignment</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/customer-consignment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/customer-consignment/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -20560,7 +20560,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/customer-consignment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -20577,17 +20577,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t xml:space="preserve">External Procurement</t>
+          <t xml:space="preserve">Customer Consignment</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/external-procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/customer-consignment/</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/external-procurement/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/customer-consignment/index.html</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/external-procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/customer-consignment/</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -20642,17 +20642,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immediate Sales</t>
+          <t xml:space="preserve">External Procurement</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/immediate-sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/external-procurement/</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/immediate-sales/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/external-procurement/index.html</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/immediate-sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/external-procurement/</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -20707,22 +20707,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Processes</t>
+          <t xml:space="preserve">Immediate Sales</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/immediate-sales/</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/immediate-sales/index.html</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -20732,14 +20732,14 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
           <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I259" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
@@ -20755,7 +20755,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/immediate-sales/</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -20767,27 +20767,27 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Sales Processes</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -20797,12 +20797,12 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -20832,22 +20832,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intercompany Sales</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/intercompany-sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/intercompany-sales/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">integration-patterns, sales-o2c</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -20885,7 +20885,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/intercompany-sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -20902,17 +20902,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make To Order</t>
+          <t xml:space="preserve">Intercompany Sales</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/make-to-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/intercompany-sales/</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/make-to-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/intercompany-sales/index.html</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/make-to-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/intercompany-sales/</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -20962,27 +20962,27 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Make To Order</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/make-to-order/</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/make-to-order/index.html</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -20992,14 +20992,14 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
           <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I263" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/make-to-order/</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -21027,27 +21027,27 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -21057,12 +21057,12 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -21097,17 +21097,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -21145,7 +21145,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -21162,17 +21162,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Free Of Charge</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/returns-free-of-charge/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -21227,17 +21227,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stock Transfer Orders</t>
+          <t xml:space="preserve">Returns Free Of Charge</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/stock-transfer-orders/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/returns-free-of-charge/index.html</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -21275,7 +21275,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -21287,27 +21287,27 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Shipping</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping</t>
+          <t xml:space="preserve">Stock Transfer Orders</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/stock-transfer-orders/index.html</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -21317,12 +21317,12 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -21352,27 +21352,27 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP Shipping</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Shipping</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -21382,12 +21382,12 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-shipping</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -21417,42 +21417,42 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -21482,42 +21482,42 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -21535,7 +21535,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -21552,22 +21552,22 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Management</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -21577,17 +21577,17 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J272" t="n">
@@ -21600,7 +21600,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -21612,27 +21612,27 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Transportation Management</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -21642,17 +21642,17 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J273" t="n">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -21677,22 +21677,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">integration-patterns, sales-o2c</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -21742,27 +21742,27 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erp Diagnostic Practice</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -21772,12 +21772,12 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -21812,17 +21812,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
+          <t xml:space="preserve">Erp Diagnostic Practice</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
+          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -21832,12 +21832,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -21872,42 +21872,42 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-ams, delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -21925,7 +21925,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -21937,42 +21937,42 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/index.md</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, delivery-ams, delivery-memory</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -21990,7 +21990,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -22007,17 +22007,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -22032,7 +22032,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -22055,7 +22055,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -22072,17 +22072,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -22137,17 +22137,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -22185,7 +22185,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -22202,17 +22202,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -22227,7 +22227,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -22250,7 +22250,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -22262,22 +22262,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -22292,7 +22292,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -22315,7 +22315,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -22327,42 +22327,42 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -22397,37 +22397,37 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -22462,17 +22462,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22510,7 +22510,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -22527,37 +22527,37 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-ams, logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -22592,17 +22592,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">sales-o2c, delivery-ams, logistics-tm</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -22657,17 +22657,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-ams</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -22705,7 +22705,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -22722,17 +22722,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -22752,7 +22752,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-ams</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -22787,17 +22787,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -22852,37 +22852,37 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -22912,42 +22912,42 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -22965,7 +22965,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -22977,27 +22977,27 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -23007,17 +23007,17 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J294" t="n">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -23042,37 +23042,37 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/templates/</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/templates/index.md</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -23107,70 +23107,135 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J296" t="n">
+        <v>1</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
+      <c r="C297" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
+      <c r="D297" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
+      <c r="E297" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
+      <c r="F297" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
+      <c r="G297" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, sales-o2c, ai-agents-mcp</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J296" t="n">
-        <v>1</v>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L296" t="inlineStr">
+      <c r="I297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J297" t="n">
+        <v>1</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M296" t="inlineStr">
+      <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M296"/>
+  <autoFilter ref="A1:M297"/>
 </worksheet>
 </file>
 
@@ -24814,10 +24879,10 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" t="n">
         <v>2</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.5%</t>
+          <t xml:space="preserve">37.7%</t>
         </is>
       </c>
     </row>
@@ -1639,6 +1639,7 @@
       <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">Procurement — https://dkharlanau.github.io/labs/enterprise-context/procurement/
+MRP 2 Procurement Controls — https://dkharlanau.github.io/labs/enterprise-context/procurement/mrp2-procurement-controls/
 Material Valuation — https://dkharlanau.github.io/labs/enterprise-context/procurement/material-valuation/
 Condition Contract Management — https://dkharlanau.github.io/labs/enterprise-context/condition-contract-management/
 Kanban Replenishment Strategies — https://dkharlanau.github.io/labs/enterprise-context/kanban/replenishment-strategies/
@@ -1782,6 +1783,7 @@
           <t xml:space="preserve">ERP Diagnostic Practice — https://dkharlanau.github.io/labs/erp-diagnostic-practice/
 Material Behaviour — https://dkharlanau.github.io/labs/enterprise-context/material-behavior/
 Master Data — https://dkharlanau.github.io/labs/enterprise-context/master-data/
+MRP 2 Procurement Controls — https://dkharlanau.github.io/labs/enterprise-context/procurement/mrp2-procurement-controls/
 Sales BOM / Product Structure — https://dkharlanau.github.io/labs/enterprise-context/master-data/sales-bom/
 Variant Configuration — https://dkharlanau.github.io/labs/enterprise-context/master-data/variant-configuration/
 Business Partner API — https://dkharlanau.github.io/labs/enterprise-context/integrations/business-partner-api/
@@ -1982,6 +1984,7 @@
       <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">Production — https://dkharlanau.github.io/labs/enterprise-context/production/
+MRP 2 Procurement Controls — https://dkharlanau.github.io/labs/enterprise-context/procurement/mrp2-procurement-controls/
 Variant Configuration — https://dkharlanau.github.io/labs/enterprise-context/master-data/variant-configuration/
 Quality Management — https://dkharlanau.github.io/labs/enterprise-context/quality-management/
 SAP Kanban — https://dkharlanau.github.io/labs/enterprise-context/kanban/
@@ -6567,7 +6570,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, integration-ownership, logistics-p2p</t>
+          <t xml:space="preserve">sales-o2c, integration-ownership, logistics-master-data</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -7672,7 +7675,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-testing, integration-observability</t>
+          <t xml:space="preserve">logistics-master-data, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -7737,7 +7740,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, sales-o2c, ai-readiness</t>
+          <t xml:space="preserve">integration-recovery, logistics-master-data, sales-o2c</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -8517,7 +8520,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-readiness, ai-data-governance</t>
+          <t xml:space="preserve">ai-agents-mcp, ai-readiness, logistics-master-data</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -10012,7 +10015,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, logistics-production-quality</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -12092,7 +12095,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, logistics-ewm, sales-o2c</t>
+          <t xml:space="preserve">ai-readiness, logistics-ewm, logistics-master-data</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -17552,7 +17555,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-lifecycle</t>
+          <t xml:space="preserve">logistics-production-quality, logistics-master-data, logistics-tm</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -19407,37 +19410,37 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchasing Customizing</t>
+          <t xml:space="preserve">SAP MRP 2 — Procurement Types, Special Procurement and Storage Locations</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/purchasing-customizing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/mrp2-procurement-controls/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/purchasing-customizing/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/mrp2-procurement-controls/index.md</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, logistics-production-quality</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -19455,7 +19458,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/purchasing-customizing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/mrp2-procurement-controls/</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19472,37 +19475,37 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
+          <t xml:space="preserve">Purchasing Customizing</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/purchasing-customizing/</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/purchasing-customizing/index.html</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, logistics-production-quality</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -19520,7 +19523,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/purchasing-customizing/</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19537,17 +19540,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -19562,7 +19565,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -19585,7 +19588,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -19602,17 +19605,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -19627,7 +19630,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -19650,7 +19653,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19667,17 +19670,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -19692,7 +19695,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19715,7 +19718,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19732,17 +19735,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
+          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -19757,7 +19760,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19780,7 +19783,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19797,37 +19800,37 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax Code Determination in Purchasing &amp; Invoice Receipt — SAP S/4HANA MM</t>
+          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/tax-code-determination/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/tax-code-determination/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, delivery-testing, integration-development</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -19845,7 +19848,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/tax-code-determination/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19857,42 +19860,42 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Production / PP</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consumption-Based Planning &amp; Forecasting — SAP S/4HANA MRP</t>
+          <t xml:space="preserve">Tax Code Determination in Purchasing &amp; Invoice Receipt — SAP S/4HANA MM</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/production/consumption-based-planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/tax-code-determination/</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/production/consumption-based-planning.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/tax-code-determination/index.md</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p, logistics-production-quality</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-p2p, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -19910,7 +19913,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/consumption-based-planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/tax-code-determination/</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19927,17 +19930,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production</t>
+          <t xml:space="preserve">Consumption-Based Planning &amp; Forecasting — SAP S/4HANA MRP</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/consumption-based-planning/</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/consumption-based-planning.md</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -19947,12 +19950,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, logistics-production-quality</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -19962,7 +19965,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J247" t="n">
@@ -19975,7 +19978,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/consumption-based-planning/</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19987,22 +19990,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Quality Management</t>
+          <t xml:space="preserve">SAP Production / PP</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality Management</t>
+          <t xml:space="preserve">Production</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20040,7 +20043,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20052,27 +20055,27 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Quality Management</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Quality Management</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -20082,17 +20085,17 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, ai-evaluation, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J249" t="n">
@@ -20105,7 +20108,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20117,27 +20120,27 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -20147,17 +20150,17 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-diagnostics</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, ai-evaluation, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J250" t="n">
@@ -20170,7 +20173,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -20182,22 +20185,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Diagnostics</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -20235,7 +20238,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -20247,22 +20250,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Fiori Apps</t>
+          <t xml:space="preserve">Sales Diagnostics</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-fiori-apps/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-fiori-apps/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -20277,7 +20280,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -20287,7 +20290,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J252" t="n">
@@ -20300,7 +20303,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-fiori-apps/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -20312,27 +20315,27 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Sales Fiori Apps</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-fiori-apps/</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-fiori-apps/index.html</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -20342,12 +20345,12 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -20365,7 +20368,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-fiori-apps/</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -20382,17 +20385,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -20430,7 +20433,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -20447,17 +20450,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -20495,7 +20498,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -20512,17 +20515,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -20542,7 +20545,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -20560,7 +20563,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -20577,17 +20580,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customer Consignment</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/customer-consignment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/customer-consignment/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -20607,7 +20610,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -20625,7 +20628,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/customer-consignment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -20642,17 +20645,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t xml:space="preserve">External Procurement</t>
+          <t xml:space="preserve">Customer Consignment</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/external-procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/customer-consignment/</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/external-procurement/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/customer-consignment/index.html</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -20690,7 +20693,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/external-procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/customer-consignment/</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -20707,17 +20710,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immediate Sales</t>
+          <t xml:space="preserve">External Procurement</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/immediate-sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/external-procurement/</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/immediate-sales/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/external-procurement/index.html</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -20755,7 +20758,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/immediate-sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/external-procurement/</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -20772,22 +20775,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Processes</t>
+          <t xml:space="preserve">Immediate Sales</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/immediate-sales/</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/immediate-sales/index.html</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -20797,14 +20800,14 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
           <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I260" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
@@ -20820,7 +20823,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/immediate-sales/</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -20832,27 +20835,27 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Sales Processes</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -20862,12 +20865,12 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -20885,7 +20888,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -20897,22 +20900,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intercompany Sales</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/intercompany-sales/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/intercompany-sales/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -20932,7 +20935,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">integration-patterns, sales-o2c</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -20950,7 +20953,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/intercompany-sales/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -20967,17 +20970,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make To Order</t>
+          <t xml:space="preserve">Intercompany Sales</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/make-to-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/intercompany-sales/</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/make-to-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/intercompany-sales/index.html</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -21015,7 +21018,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/make-to-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/intercompany-sales/</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -21027,27 +21030,27 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Make To Order</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/make-to-order/</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/make-to-order/index.html</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -21057,14 +21060,14 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
           <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I264" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
@@ -21080,7 +21083,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/make-to-order/</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -21092,27 +21095,27 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -21122,12 +21125,12 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -21145,7 +21148,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -21162,17 +21165,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -21210,7 +21213,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -21227,17 +21230,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Free Of Charge</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/returns-free-of-charge/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -21275,7 +21278,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -21292,17 +21295,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stock Transfer Orders</t>
+          <t xml:space="preserve">Returns Free Of Charge</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/stock-transfer-orders/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/returns-free-of-charge/index.html</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -21340,7 +21343,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/returns-free-of-charge/</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -21352,27 +21355,27 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Shipping</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping</t>
+          <t xml:space="preserve">Stock Transfer Orders</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/stock-transfer-orders/index.html</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -21382,12 +21385,12 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -21405,7 +21408,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/stock-transfer-orders/</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -21417,27 +21420,27 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP Shipping</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Shipping</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -21447,12 +21450,12 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-shipping</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -21470,7 +21473,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -21482,42 +21485,42 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -21535,7 +21538,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -21547,42 +21550,42 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -21600,7 +21603,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -21617,22 +21620,22 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Management</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -21642,17 +21645,17 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J273" t="n">
@@ -21665,7 +21668,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -21677,27 +21680,27 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Transportation Management</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -21707,17 +21710,17 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J274" t="n">
@@ -21730,7 +21733,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -21742,22 +21745,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -21777,7 +21780,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">integration-patterns, sales-o2c</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -21795,7 +21798,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -21807,27 +21810,27 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erp Diagnostic Practice</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -21837,12 +21840,12 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -21860,7 +21863,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -21877,17 +21880,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
+          <t xml:space="preserve">Erp Diagnostic Practice</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
+          <t xml:space="preserve">labs/erp-diagnostic-practice/index.html</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -21897,12 +21900,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-master-data</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -21925,7 +21928,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/erp-diagnostic-practice/</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -21937,42 +21940,42 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-ams, delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -21990,7 +21993,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -22002,42 +22005,42 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/index.md</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c, delivery-ams, delivery-memory</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -22055,7 +22058,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -22072,17 +22075,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -22097,7 +22100,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -22120,7 +22123,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -22137,17 +22140,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -22162,7 +22165,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -22185,7 +22188,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -22202,17 +22205,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -22227,7 +22230,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -22250,7 +22253,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -22267,17 +22270,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -22292,7 +22295,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -22315,7 +22318,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -22327,22 +22330,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -22357,7 +22360,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22380,7 +22383,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -22392,42 +22395,42 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -22445,7 +22448,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -22462,37 +22465,37 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -22510,7 +22513,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -22527,17 +22530,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -22552,7 +22555,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -22575,7 +22578,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -22592,37 +22595,37 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-ams, logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -22640,7 +22643,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -22657,17 +22660,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -22687,7 +22690,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve">sales-o2c, delivery-ams, logistics-tm</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -22705,7 +22708,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -22722,17 +22725,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -22752,7 +22755,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-ams</t>
+          <t xml:space="preserve">lead-evidence, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -22770,7 +22773,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -22787,17 +22790,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -22817,7 +22820,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
+          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-ams</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -22835,7 +22838,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -22852,17 +22855,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -22882,7 +22885,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-o2c</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -22900,7 +22903,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -22917,37 +22920,37 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -22965,7 +22968,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -22977,42 +22980,42 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -23030,7 +23033,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -23042,27 +23045,27 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -23072,17 +23075,17 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J295" t="n">
@@ -23095,7 +23098,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -23107,37 +23110,37 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/templates/</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/templates/index.md</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -23160,7 +23163,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -23172,70 +23175,135 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J297" t="n">
+        <v>1</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
+      <c r="B298" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
+      <c r="C298" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
+      <c r="D298" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
+      <c r="E298" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
+      <c r="F298" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
+      <c r="G298" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, sales-o2c, ai-agents-mcp</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J297" t="n">
-        <v>1</v>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
+      <c r="I298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J298" t="n">
+        <v>1</v>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M297" t="inlineStr">
+      <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M297"/>
+  <autoFilter ref="A1:M298"/>
 </worksheet>
 </file>
 
@@ -24857,10 +24925,10 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
@@ -26732,7 +26800,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, integration-ownership, logistics-p2p</t>
+          <t xml:space="preserve">sales-o2c, integration-ownership, logistics-master-data</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -27176,7 +27244,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, delivery-testing, integration-observability</t>
+          <t xml:space="preserve">logistics-master-data, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -27213,7 +27281,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, sales-o2c, ai-readiness</t>
+          <t xml:space="preserve">integration-recovery, logistics-master-data, sales-o2c</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -27472,7 +27540,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-agents-mcp, ai-readiness, ai-data-governance</t>
+          <t xml:space="preserve">ai-agents-mcp, ai-readiness, logistics-master-data</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -27879,7 +27947,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, logistics-production-quality</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -28878,7 +28946,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, logistics-ewm, sales-o2c</t>
+          <t xml:space="preserve">ai-readiness, logistics-ewm, logistics-master-data</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -30654,7 +30722,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, sales-o2c, delivery-lifecycle</t>
+          <t xml:space="preserve">logistics-production-quality, logistics-master-data, logistics-tm</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -31135,7 +31203,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, logistics-production-quality</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
